--- a/knowledge/exhibits/Rent_Chart_Data.xlsx
+++ b/knowledge/exhibits/Rent_Chart_Data.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="439">
   <si>
     <t xml:space="preserve">Monthly T90 (trailing-90-day) Mix-Weighted HelloData Asking Rent</t>
   </si>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">SEASONS T90 MIX-WEIGHTED</t>
   </si>
   <si>
-    <t xml:space="preserve">PRELUDE AT PARAMOUNT (populates when Unit Details pasted on HD_Prelude)</t>
+    <t xml:space="preserve">PRELUDE AT PARAMOUNT (HD Unit Details, pull 8/13/2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Fallback (RR avg rent)</t>
@@ -98,13 +98,13 @@
     <t xml:space="preserve">PRELUDE T90 MIX-WEIGHTED</t>
   </si>
   <si>
-    <t xml:space="preserve">Data-status flag (0 = no Prelude unit details pasted yet):</t>
+    <t xml:space="preserve">Data-status flag (count of Prelude lease records loaded):</t>
   </si>
   <si>
     <t xml:space="preserve">Chart Data — monthly</t>
   </si>
   <si>
-    <t xml:space="preserve">Green = live formulas (T90_Monthly / L5 tabs). Blue = extracted (models/statements). Prelude T90 column stays blank until the Unit Details export is pasted on HD_Prelude.</t>
+    <t xml:space="preserve">Green = live formulas (T90_Monthly / L5 tabs). Blue = extracted (models/statements). Both T90 series computed from lease-level HelloData on HD_Seasons / HD_Prelude.</t>
   </si>
   <si>
     <t xml:space="preserve">Date</t>
@@ -1214,19 +1214,37 @@
     <t xml:space="preserve">Floorplan (raw)</t>
   </si>
   <si>
-    <t xml:space="preserve">PASTE the Prelude HelloData UNIT DETAILS export (lease-level) into columns B:E starting row 2 — floorplan, SF, off-market date, last asking rent. Column F maps by SF (787/1092/1172/1291). The T90_Monthly Prelude grid and Chart_Data populate automatically. The unit-TYPE table export (aggregates) cannot be used — it has no dates.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">example: A1- 1 Bedroom 1 Bath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/15/26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,450</t>
+    <t xml:space="preserve">381 lease records — Prelude HelloData Unit Details export, pull 8/13/2026. Column F maps floor plan by SF (787/1092/1172/1291). Rows below the data are spare mapping formulas so a refreshed export can be pasted over columns B:E.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1- 1 Bedroom 1 Bath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Donnelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1- 2 Bedroom 2 Bath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Ketchum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2x2 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B2- 2 Bedroom 2 Bath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The McCall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1- 3 Bedroom 2 Bath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sun Valley</t>
   </si>
   <si>
     <t xml:space="preserve">Last-5 New Leases — Seasons model methodology</t>
@@ -3133,107 +3151,107 @@
       </c>
       <c r="E20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(E$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;E$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(E$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;E$4),$D20)</f>
-        <v>1431</v>
+        <v>1363.91304347826</v>
       </c>
       <c r="F20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(F$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;F$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(F$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;F$4),E20)</f>
-        <v>1431</v>
+        <v>1354.75</v>
       </c>
       <c r="G20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(G$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;G$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(G$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;G$4),F20)</f>
-        <v>1431</v>
+        <v>1372.66666666667</v>
       </c>
       <c r="H20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(H$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;H$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(H$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;H$4),G20)</f>
-        <v>1431</v>
+        <v>1511.66666666667</v>
       </c>
       <c r="I20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(I$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;I$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(I$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;I$4),H20)</f>
-        <v>1431</v>
+        <v>1457</v>
       </c>
       <c r="J20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(J$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;J$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(J$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;J$4),I20)</f>
-        <v>1431</v>
+        <v>1369.375</v>
       </c>
       <c r="K20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(K$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;K$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(K$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;K$4),J20)</f>
-        <v>1431</v>
+        <v>1345.33333333333</v>
       </c>
       <c r="L20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(L$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;L$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(L$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;L$4),K20)</f>
-        <v>1431</v>
+        <v>1334.375</v>
       </c>
       <c r="M20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(M$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;M$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(M$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;M$4),L20)</f>
-        <v>1431</v>
+        <v>1341.5</v>
       </c>
       <c r="N20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(N$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;N$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(N$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;N$4),M20)</f>
-        <v>1431</v>
+        <v>1353</v>
       </c>
       <c r="O20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(O$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;O$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(O$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;O$4),N20)</f>
-        <v>1431</v>
+        <v>1437.27272727273</v>
       </c>
       <c r="P20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(P$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;P$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(P$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;P$4),O20)</f>
-        <v>1431</v>
+        <v>1439.375</v>
       </c>
       <c r="Q20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Q$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Q$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Q$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Q$4),P20)</f>
-        <v>1431</v>
+        <v>1461</v>
       </c>
       <c r="R20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(R$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;R$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(R$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;R$4),Q20)</f>
-        <v>1431</v>
+        <v>1459.41666666667</v>
       </c>
       <c r="S20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(S$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;S$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(S$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;S$4),R20)</f>
-        <v>1431</v>
+        <v>1464.77777777778</v>
       </c>
       <c r="T20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(T$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;T$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(T$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;T$4),S20)</f>
-        <v>1431</v>
+        <v>1439.75</v>
       </c>
       <c r="U20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(U$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;U$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(U$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;U$4),T20)</f>
-        <v>1431</v>
+        <v>1450.71428571429</v>
       </c>
       <c r="V20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(V$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;V$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(V$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;V$4),U20)</f>
-        <v>1431</v>
+        <v>1460.55555555556</v>
       </c>
       <c r="W20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(W$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;W$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(W$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;W$4),V20)</f>
-        <v>1431</v>
+        <v>1460.71428571429</v>
       </c>
       <c r="X20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(X$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;X$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(X$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;X$4),W20)</f>
-        <v>1431</v>
+        <v>1459</v>
       </c>
       <c r="Y20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Y$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Y$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Y$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Y$4),X20)</f>
-        <v>1431</v>
+        <v>1408.66666666667</v>
       </c>
       <c r="Z20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Z$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Z$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Z$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Z$4),Y20)</f>
-        <v>1431</v>
+        <v>1421.47058823529</v>
       </c>
       <c r="AA20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AA$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AA$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AA$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AA$4),Z20)</f>
-        <v>1431</v>
+        <v>1449.07407407407</v>
       </c>
       <c r="AB20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AB$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AB$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AB$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AB$4),AA20)</f>
-        <v>1431</v>
+        <v>1470.875</v>
       </c>
       <c r="AC20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AC$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AC$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AC$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AC$4),AB20)</f>
-        <v>1431</v>
+        <v>1512.35714285714</v>
       </c>
       <c r="AD20" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AD$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AD$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B20,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AD$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AD$4),AC20)</f>
-        <v>1431</v>
+        <v>1561.14285714286</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3248,107 +3266,107 @@
       </c>
       <c r="E21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(E$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;E$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(E$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;E$4),$D21)</f>
-        <v>1733</v>
+        <v>1730</v>
       </c>
       <c r="F21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(F$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;F$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(F$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;F$4),E21)</f>
-        <v>1733</v>
+        <v>1786.25</v>
       </c>
       <c r="G21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(G$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;G$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(G$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;G$4),F21)</f>
-        <v>1733</v>
+        <v>1802.14285714286</v>
       </c>
       <c r="H21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(H$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;H$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(H$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;H$4),G21)</f>
-        <v>1733</v>
+        <v>1830</v>
       </c>
       <c r="I21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(I$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;I$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(I$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;I$4),H21)</f>
-        <v>1733</v>
+        <v>1683</v>
       </c>
       <c r="J21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(J$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;J$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(J$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;J$4),I21)</f>
-        <v>1733</v>
+        <v>1629.28571428571</v>
       </c>
       <c r="K21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(K$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;K$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(K$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;K$4),J21)</f>
-        <v>1733</v>
+        <v>1654.16666666667</v>
       </c>
       <c r="L21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(L$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;L$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(L$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;L$4),K21)</f>
-        <v>1733</v>
+        <v>1670</v>
       </c>
       <c r="M21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(M$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;M$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(M$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;M$4),L21)</f>
-        <v>1733</v>
+        <v>1681.76470588235</v>
       </c>
       <c r="N21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(N$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;N$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(N$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;N$4),M21)</f>
-        <v>1733</v>
+        <v>1684.09090909091</v>
       </c>
       <c r="O21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(O$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;O$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(O$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;O$4),N21)</f>
-        <v>1733</v>
+        <v>1703</v>
       </c>
       <c r="P21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(P$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;P$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(P$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;P$4),O21)</f>
-        <v>1733</v>
+        <v>1718.21428571429</v>
       </c>
       <c r="Q21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Q$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Q$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Q$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Q$4),P21)</f>
-        <v>1733</v>
+        <v>1831.66666666667</v>
       </c>
       <c r="R21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(R$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;R$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(R$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;R$4),Q21)</f>
-        <v>1733</v>
+        <v>1813.77777777778</v>
       </c>
       <c r="S21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(S$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;S$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(S$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;S$4),R21)</f>
-        <v>1733</v>
+        <v>1811.4</v>
       </c>
       <c r="T21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(T$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;T$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(T$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;T$4),S21)</f>
-        <v>1733</v>
+        <v>1791.75</v>
       </c>
       <c r="U21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(U$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;U$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(U$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;U$4),T21)</f>
-        <v>1733</v>
+        <v>1794</v>
       </c>
       <c r="V21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(V$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;V$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(V$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;V$4),U21)</f>
-        <v>1733</v>
+        <v>1779.8</v>
       </c>
       <c r="W21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(W$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;W$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(W$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;W$4),V21)</f>
-        <v>1733</v>
+        <v>1771</v>
       </c>
       <c r="X21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(X$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;X$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(X$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;X$4),W21)</f>
-        <v>1733</v>
+        <v>1719</v>
       </c>
       <c r="Y21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Y$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Y$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Y$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Y$4),X21)</f>
-        <v>1733</v>
+        <v>1690</v>
       </c>
       <c r="Z21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Z$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Z$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Z$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Z$4),Y21)</f>
-        <v>1733</v>
+        <v>1720.11111111111</v>
       </c>
       <c r="AA21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AA$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AA$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AA$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AA$4),Z21)</f>
-        <v>1733</v>
+        <v>1740</v>
       </c>
       <c r="AB21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AB$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AB$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AB$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AB$4),AA21)</f>
-        <v>1733</v>
+        <v>1760.94736842105</v>
       </c>
       <c r="AC21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AC$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AC$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AC$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AC$4),AB21)</f>
-        <v>1733</v>
+        <v>1815.82352941176</v>
       </c>
       <c r="AD21" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AD$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AD$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B21,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AD$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AD$4),AC21)</f>
-        <v>1733</v>
+        <v>1833.875</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3363,107 +3381,107 @@
       </c>
       <c r="E22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(E$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;E$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(E$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;E$4),$D22)</f>
-        <v>1767</v>
+        <v>1837</v>
       </c>
       <c r="F22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(F$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;F$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(F$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;F$4),E22)</f>
-        <v>1767</v>
+        <v>1838.33333333333</v>
       </c>
       <c r="G22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(G$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;G$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(G$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;G$4),F22)</f>
-        <v>1767</v>
+        <v>1818.33333333333</v>
       </c>
       <c r="H22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(H$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;H$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(H$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;H$4),G22)</f>
-        <v>1767</v>
+        <v>1685</v>
       </c>
       <c r="I22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(I$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;I$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(I$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;I$4),H22)</f>
-        <v>1767</v>
+        <v>1668.75</v>
       </c>
       <c r="J22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(J$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;J$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(J$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;J$4),I22)</f>
-        <v>1767</v>
+        <v>1643</v>
       </c>
       <c r="K22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(K$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;K$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(K$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;K$4),J22)</f>
-        <v>1767</v>
+        <v>1645</v>
       </c>
       <c r="L22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(L$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;L$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(L$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;L$4),K22)</f>
-        <v>1767</v>
+        <v>1657.5</v>
       </c>
       <c r="M22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(M$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;M$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(M$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;M$4),L22)</f>
-        <v>1767</v>
+        <v>1657.5</v>
       </c>
       <c r="N22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(N$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;N$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(N$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;N$4),M22)</f>
-        <v>1767</v>
+        <v>1840</v>
       </c>
       <c r="O22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(O$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;O$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(O$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;O$4),N22)</f>
-        <v>1767</v>
+        <v>1792.5</v>
       </c>
       <c r="P22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(P$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;P$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(P$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;P$4),O22)</f>
-        <v>1767</v>
+        <v>1797.22222222222</v>
       </c>
       <c r="Q22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Q$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Q$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Q$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Q$4),P22)</f>
-        <v>1767</v>
+        <v>1792.5</v>
       </c>
       <c r="R22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(R$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;R$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(R$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;R$4),Q22)</f>
-        <v>1767</v>
+        <v>1838.33333333333</v>
       </c>
       <c r="S22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(S$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;S$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(S$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;S$4),R22)</f>
-        <v>1767</v>
+        <v>1838.33333333333</v>
       </c>
       <c r="T22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(T$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;T$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(T$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;T$4),S22)</f>
-        <v>1767</v>
+        <v>1820</v>
       </c>
       <c r="U22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(U$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;U$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(U$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;U$4),T22)</f>
-        <v>1767</v>
+        <v>1812.5</v>
       </c>
       <c r="V22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(V$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;V$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(V$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;V$4),U22)</f>
-        <v>1767</v>
+        <v>1800</v>
       </c>
       <c r="W22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(W$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;W$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(W$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;W$4),V22)</f>
-        <v>1767</v>
+        <v>1810</v>
       </c>
       <c r="X22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(X$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;X$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(X$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;X$4),W22)</f>
-        <v>1767</v>
+        <v>1810</v>
       </c>
       <c r="Y22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Y$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Y$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Y$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Y$4),X22)</f>
-        <v>1767</v>
+        <v>1760</v>
       </c>
       <c r="Z22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Z$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Z$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Z$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Z$4),Y22)</f>
-        <v>1767</v>
+        <v>1749.75</v>
       </c>
       <c r="AA22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AA$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AA$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AA$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AA$4),Z22)</f>
-        <v>1767</v>
+        <v>1759.66666666667</v>
       </c>
       <c r="AB22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AB$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AB$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AB$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AB$4),AA22)</f>
-        <v>1767</v>
+        <v>1781.125</v>
       </c>
       <c r="AC22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AC$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AC$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AC$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AC$4),AB22)</f>
-        <v>1767</v>
+        <v>1846.44444444444</v>
       </c>
       <c r="AD22" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AD$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AD$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B22,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AD$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AD$4),AC22)</f>
-        <v>1767</v>
+        <v>1859.5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3478,107 +3496,107 @@
       </c>
       <c r="E23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(E$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;E$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(E$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;E$4),$D23)</f>
-        <v>1984</v>
+        <v>1910</v>
       </c>
       <c r="F23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(F$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;F$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(F$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;F$4),E23)</f>
-        <v>1984</v>
+        <v>2125</v>
       </c>
       <c r="G23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(G$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;G$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(G$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;G$4),F23)</f>
-        <v>1984</v>
+        <v>2125</v>
       </c>
       <c r="H23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(H$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;H$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(H$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;H$4),G23)</f>
-        <v>1984</v>
+        <v>2175</v>
       </c>
       <c r="I23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(I$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;I$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(I$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;I$4),H23)</f>
-        <v>1984</v>
+        <v>2125</v>
       </c>
       <c r="J23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(J$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;J$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(J$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;J$4),I23)</f>
-        <v>1984</v>
+        <v>2030</v>
       </c>
       <c r="K23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(K$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;K$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(K$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;K$4),J23)</f>
-        <v>1984</v>
+        <v>2030</v>
       </c>
       <c r="L23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(L$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;L$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(L$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;L$4),K23)</f>
-        <v>1984</v>
+        <v>2030</v>
       </c>
       <c r="M23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(M$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;M$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(M$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;M$4),L23)</f>
-        <v>1984</v>
+        <v>2030</v>
       </c>
       <c r="N23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(N$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;N$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(N$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;N$4),M23)</f>
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="O23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(O$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;O$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(O$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;O$4),N23)</f>
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="P23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(P$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;P$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(P$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;P$4),O23)</f>
-        <v>1984</v>
+        <v>2078.57142857143</v>
       </c>
       <c r="Q23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Q$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Q$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Q$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Q$4),P23)</f>
-        <v>1984</v>
+        <v>2082.5</v>
       </c>
       <c r="R23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(R$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;R$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(R$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;R$4),Q23)</f>
-        <v>1984</v>
+        <v>2091.25</v>
       </c>
       <c r="S23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(S$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;S$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(S$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;S$4),R23)</f>
-        <v>1984</v>
+        <v>2088.33333333333</v>
       </c>
       <c r="T23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(T$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;T$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(T$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;T$4),S23)</f>
-        <v>1984</v>
+        <v>2081</v>
       </c>
       <c r="U23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(U$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;U$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(U$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;U$4),T23)</f>
-        <v>1984</v>
+        <v>1970</v>
       </c>
       <c r="V23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(V$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;V$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(V$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;V$4),U23)</f>
-        <v>1984</v>
+        <v>2052.5</v>
       </c>
       <c r="W23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(W$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;W$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(W$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;W$4),V23)</f>
-        <v>1984</v>
+        <v>2135</v>
       </c>
       <c r="X23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(X$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;X$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(X$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;X$4),W23)</f>
-        <v>1984</v>
+        <v>2135</v>
       </c>
       <c r="Y23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Y$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Y$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Y$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Y$4),X23)</f>
-        <v>1984</v>
+        <v>1932</v>
       </c>
       <c r="Z23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Z$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Z$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(Z$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;Z$4),Y23)</f>
-        <v>1984</v>
+        <v>1983.5</v>
       </c>
       <c r="AA23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AA$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AA$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AA$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AA$4),Z23)</f>
-        <v>1984</v>
+        <v>2017.71428571429</v>
       </c>
       <c r="AB23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AB$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AB$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AB$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AB$4),AA23)</f>
-        <v>1984</v>
+        <v>2103.71428571429</v>
       </c>
       <c r="AC23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AC$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AC$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AC$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AC$4),AB23)</f>
-        <v>1984</v>
+        <v>2218.25</v>
       </c>
       <c r="AD23" s="11" t="n">
         <f aca="false">IF(COUNTIFS(HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AD$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AD$4)&gt;0,AVERAGEIFS(HD_Prelude!$E:$E,HD_Prelude!$F:$F,$B23,HD_Prelude!$D:$D,"&gt;="&amp;EDATE(AD$4,-3)+1,HD_Prelude!$D:$D,"&lt;="&amp;AD$4),AC23)</f>
-        <v>1984</v>
+        <v>2211.4</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3587,107 +3605,107 @@
       </c>
       <c r="E24" s="12" t="n">
         <f aca="false">SUMPRODUCT(E20:E23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1631.1599378882</v>
       </c>
       <c r="F24" s="12" t="n">
         <f aca="false">SUMPRODUCT(F20:F23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1681.70892857143</v>
       </c>
       <c r="G24" s="12" t="n">
         <f aca="false">SUMPRODUCT(G20:G23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1692.02482993197</v>
       </c>
       <c r="H24" s="12" t="n">
         <f aca="false">SUMPRODUCT(H20:H23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1748.16666666667</v>
       </c>
       <c r="I24" s="12" t="n">
         <f aca="false">SUMPRODUCT(I20:I23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1665.37321428571</v>
       </c>
       <c r="J24" s="12" t="n">
         <f aca="false">SUMPRODUCT(J20:J23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1595.32971938776</v>
       </c>
       <c r="K24" s="12" t="n">
         <f aca="false">SUMPRODUCT(K20:K23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1595.32857142857</v>
       </c>
       <c r="L24" s="12" t="n">
         <f aca="false">SUMPRODUCT(L20:L23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1598.17410714286</v>
       </c>
       <c r="M24" s="12" t="n">
         <f aca="false">SUMPRODUCT(M20:M23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1605.0731092437</v>
       </c>
       <c r="N24" s="12" t="n">
         <f aca="false">SUMPRODUCT(N20:N23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1622.73961038961</v>
       </c>
       <c r="O24" s="12" t="n">
         <f aca="false">SUMPRODUCT(O20:O23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1656.30681818182</v>
       </c>
       <c r="P24" s="12" t="n">
         <f aca="false">SUMPRODUCT(P20:P23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1677.74638605442</v>
       </c>
       <c r="Q24" s="12" t="n">
         <f aca="false">SUMPRODUCT(Q20:Q23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1726.5630952381</v>
       </c>
       <c r="R24" s="12" t="n">
         <f aca="false">SUMPRODUCT(R20:R23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1725.86051587302</v>
       </c>
       <c r="S24" s="12" t="n">
         <f aca="false">SUMPRODUCT(S20:S23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1726.58253968254</v>
       </c>
       <c r="T24" s="12" t="n">
         <f aca="false">SUMPRODUCT(T20:T23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1706.97321428571</v>
       </c>
       <c r="U24" s="12" t="n">
         <f aca="false">SUMPRODUCT(U20:U23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1693.68112244898</v>
       </c>
       <c r="V24" s="12" t="n">
         <f aca="false">SUMPRODUCT(V20:V23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1703.96031746032</v>
       </c>
       <c r="W24" s="12" t="n">
         <f aca="false">SUMPRODUCT(W20:W23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1714.91326530612</v>
       </c>
       <c r="X24" s="12" t="n">
         <f aca="false">SUMPRODUCT(X20:X23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1695.69285714286</v>
       </c>
       <c r="Y24" s="12" t="n">
         <f aca="false">SUMPRODUCT(Y20:Y23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1629.02380952381</v>
       </c>
       <c r="Z24" s="12" t="n">
         <f aca="false">SUMPRODUCT(Z20:Z23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1651.61961951447</v>
       </c>
       <c r="AA24" s="12" t="n">
         <f aca="false">SUMPRODUCT(AA20:AA23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1675.61171579743</v>
       </c>
       <c r="AB24" s="12" t="n">
         <f aca="false">SUMPRODUCT(AB20:AB23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1707.15951933405</v>
       </c>
       <c r="AC24" s="12" t="n">
         <f aca="false">SUMPRODUCT(AC20:AC23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1767.45908363345</v>
       </c>
       <c r="AD24" s="12" t="n">
         <f aca="false">SUMPRODUCT(AD20:AD23,$C20:$C23)/SUM($C20:$C23)</f>
-        <v>1661.75714285714</v>
+        <v>1792.69729591837</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3696,7 +3714,7 @@
       </c>
       <c r="D25" s="14" t="n">
         <f aca="false">COUNT(HD_Prelude!$E3:$E802)</f>
-        <v>0</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -3774,9 +3792,9 @@
         <f aca="false">T90_Monthly!E16</f>
         <v>1819.05527777778</v>
       </c>
-      <c r="F6" s="17" t="str">
+      <c r="F6" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!E24)</f>
-        <v/>
+        <v>1631.1599378882</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3787,9 +3805,9 @@
         <f aca="false">T90_Monthly!F16</f>
         <v>1831.59055555556</v>
       </c>
-      <c r="F7" s="17" t="str">
+      <c r="F7" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!F24)</f>
-        <v/>
+        <v>1681.70892857143</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3800,9 +3818,9 @@
         <f aca="false">T90_Monthly!G16</f>
         <v>1843.86589068826</v>
       </c>
-      <c r="F8" s="17" t="str">
+      <c r="F8" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!G24)</f>
-        <v/>
+        <v>1692.02482993197</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3813,9 +3831,9 @@
         <f aca="false">T90_Monthly!H16</f>
         <v>1837.88392857143</v>
       </c>
-      <c r="F9" s="17" t="str">
+      <c r="F9" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!H24)</f>
-        <v/>
+        <v>1748.16666666667</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3826,9 +3844,9 @@
         <f aca="false">T90_Monthly!I16</f>
         <v>1834.25433361751</v>
       </c>
-      <c r="F10" s="17" t="str">
+      <c r="F10" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!I24)</f>
-        <v/>
+        <v>1665.37321428571</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3839,9 +3857,9 @@
         <f aca="false">T90_Monthly!J16</f>
         <v>1729.60351107226</v>
       </c>
-      <c r="F11" s="17" t="str">
+      <c r="F11" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!J24)</f>
-        <v/>
+        <v>1595.32971938776</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3852,9 +3870,9 @@
         <f aca="false">T90_Monthly!K16</f>
         <v>1691.61111111111</v>
       </c>
-      <c r="F12" s="17" t="str">
+      <c r="F12" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!K24)</f>
-        <v/>
+        <v>1595.32857142857</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3865,9 +3883,9 @@
         <f aca="false">T90_Monthly!L16</f>
         <v>1685.9375</v>
       </c>
-      <c r="F13" s="17" t="str">
+      <c r="F13" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!L24)</f>
-        <v/>
+        <v>1598.17410714286</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3878,9 +3896,9 @@
         <f aca="false">T90_Monthly!M16</f>
         <v>1722.60892857143</v>
       </c>
-      <c r="F14" s="17" t="str">
+      <c r="F14" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!M24)</f>
-        <v/>
+        <v>1605.0731092437</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3891,9 +3909,9 @@
         <f aca="false">T90_Monthly!N16</f>
         <v>1763.53371407121</v>
       </c>
-      <c r="F15" s="17" t="str">
+      <c r="F15" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!N24)</f>
-        <v/>
+        <v>1622.73961038961</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3904,9 +3922,9 @@
         <f aca="false">T90_Monthly!O16</f>
         <v>1785.1849702381</v>
       </c>
-      <c r="F16" s="17" t="str">
+      <c r="F16" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!O24)</f>
-        <v/>
+        <v>1656.30681818182</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3917,9 +3935,9 @@
         <f aca="false">T90_Monthly!P16</f>
         <v>1800.70924272487</v>
       </c>
-      <c r="F17" s="17" t="str">
+      <c r="F17" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!P24)</f>
-        <v/>
+        <v>1677.74638605442</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3930,9 +3948,9 @@
         <f aca="false">T90_Monthly!Q16</f>
         <v>1828.86289173789</v>
       </c>
-      <c r="F18" s="17" t="str">
+      <c r="F18" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!Q24)</f>
-        <v/>
+        <v>1726.5630952381</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3943,9 +3961,9 @@
         <f aca="false">T90_Monthly!R16</f>
         <v>1809.78350284836</v>
       </c>
-      <c r="F19" s="17" t="str">
+      <c r="F19" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!R24)</f>
-        <v/>
+        <v>1725.86051587302</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3956,9 +3974,9 @@
         <f aca="false">T90_Monthly!S16</f>
         <v>1781.16535547786</v>
       </c>
-      <c r="F20" s="17" t="str">
+      <c r="F20" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!S24)</f>
-        <v/>
+        <v>1726.58253968254</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3969,9 +3987,9 @@
         <f aca="false">T90_Monthly!T16</f>
         <v>1716.34907407407</v>
       </c>
-      <c r="F21" s="17" t="str">
+      <c r="F21" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!T24)</f>
-        <v/>
+        <v>1706.97321428571</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3982,9 +4000,9 @@
         <f aca="false">T90_Monthly!U16</f>
         <v>1679.63697089947</v>
       </c>
-      <c r="F22" s="17" t="str">
+      <c r="F22" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!U24)</f>
-        <v/>
+        <v>1693.68112244898</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3995,9 +4013,9 @@
         <f aca="false">T90_Monthly!V16</f>
         <v>1676.65393518519</v>
       </c>
-      <c r="F23" s="17" t="str">
+      <c r="F23" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!V24)</f>
-        <v/>
+        <v>1703.96031746032</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4016,9 +4034,9 @@
         <f aca="false">T90_Monthly!W16</f>
         <v>1698.00978535354</v>
       </c>
-      <c r="F25" s="17" t="str">
+      <c r="F25" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!W24)</f>
-        <v/>
+        <v>1714.91326530612</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4037,9 +4055,9 @@
         <f aca="false">T90_Monthly!X16</f>
         <v>1678.38017676768</v>
       </c>
-      <c r="F27" s="17" t="str">
+      <c r="F27" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!X24)</f>
-        <v/>
+        <v>1695.69285714286</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4058,9 +4076,9 @@
         <f aca="false">T90_Monthly!Y16</f>
         <v>1722.68074770928</v>
       </c>
-      <c r="F29" s="17" t="str">
+      <c r="F29" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!Y24)</f>
-        <v/>
+        <v>1629.02380952381</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4079,9 +4097,9 @@
         <f aca="false">T90_Monthly!Z16</f>
         <v>1763.60901559454</v>
       </c>
-      <c r="F31" s="17" t="str">
+      <c r="F31" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!Z24)</f>
-        <v/>
+        <v>1651.61961951447</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4100,9 +4118,9 @@
         <f aca="false">T90_Monthly!AA16</f>
         <v>1836.23011525512</v>
       </c>
-      <c r="F33" s="17" t="str">
+      <c r="F33" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!AA24)</f>
-        <v/>
+        <v>1675.61171579743</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4121,9 +4139,9 @@
         <f aca="false">T90_Monthly!AB16</f>
         <v>1913.6579423436</v>
       </c>
-      <c r="F35" s="17" t="str">
+      <c r="F35" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!AB24)</f>
-        <v/>
+        <v>1707.15951933405</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4150,9 +4168,9 @@
         <f aca="false">T90_Monthly!AC16</f>
         <v>1934.85596405229</v>
       </c>
-      <c r="F38" s="17" t="str">
+      <c r="F38" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!AC24)</f>
-        <v/>
+        <v>1767.45908363345</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4175,9 +4193,9 @@
         <f aca="false">T90_Monthly!AD16</f>
         <v>1939.36375661376</v>
       </c>
-      <c r="F40" s="17" t="str">
+      <c r="F40" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$25=0,"",T90_Monthly!AD24)</f>
-        <v/>
+        <v>1792.69729591837</v>
       </c>
       <c r="I40" s="17" t="n">
         <f aca="false">L5_New_Leases!D44</f>
@@ -13472,2308 +13490,6856 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="18" t="s">
         <v>397</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>399</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>400</v>
+      <c r="C2" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D2" s="19" t="n">
+        <v>45408</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>1425</v>
       </c>
       <c r="F2" s="8" t="str">
         <f aca="false">IF($C2="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C2,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D3" s="19" t="n">
+        <v>46091</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>1397</v>
+      </c>
       <c r="F3" s="8" t="str">
         <f aca="false">IF($C3="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C3,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>46108</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>1397</v>
+      </c>
       <c r="F4" s="8" t="str">
         <f aca="false">IF($C4="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C4,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>45436</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>1425</v>
+      </c>
       <c r="F5" s="8" t="str">
         <f aca="false">IF($C5="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C5,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>45700</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1315</v>
+      </c>
       <c r="F6" s="8" t="str">
         <f aca="false">IF($C6="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C6,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>46102</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>1397</v>
+      </c>
       <c r="F7" s="8" t="str">
         <f aca="false">IF($C7="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C7,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>45701</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>1315</v>
+      </c>
       <c r="F8" s="8" t="str">
         <f aca="false">IF($C8="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C8,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>46123</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>1397</v>
+      </c>
       <c r="F9" s="8" t="str">
         <f aca="false">IF($C9="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C9,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>46123</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>1397</v>
+      </c>
       <c r="F10" s="8" t="str">
         <f aca="false">IF($C10="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C10,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>1397</v>
+      </c>
       <c r="F11" s="8" t="str">
         <f aca="false">IF($C11="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C11,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>1397</v>
+      </c>
       <c r="F12" s="8" t="str">
         <f aca="false">IF($C12="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C12,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>46098</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>1407</v>
+      </c>
       <c r="F13" s="8" t="str">
         <f aca="false">IF($C13="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C13,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>45313</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>1435</v>
+      </c>
       <c r="F14" s="8" t="str">
         <f aca="false">IF($C14="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C14,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>45785</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>1430</v>
+      </c>
       <c r="F15" s="8" t="str">
         <f aca="false">IF($C15="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C15,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>46091</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>1407</v>
+      </c>
       <c r="F16" s="8" t="str">
         <f aca="false">IF($C16="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C16,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>45764</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>1420</v>
+      </c>
       <c r="F17" s="8" t="str">
         <f aca="false">IF($C17="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C17,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>46136</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>1435</v>
+      </c>
       <c r="F18" s="8" t="str">
         <f aca="false">IF($C18="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C18,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>46142</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>1435</v>
+      </c>
       <c r="F19" s="8" t="str">
         <f aca="false">IF($C19="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C19,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>45272</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>1325</v>
+      </c>
       <c r="F20" s="8" t="str">
         <f aca="false">IF($C20="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C20,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>46142</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>1435</v>
+      </c>
       <c r="F21" s="8" t="str">
         <f aca="false">IF($C21="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C21,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>45662</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>1375</v>
+      </c>
       <c r="F22" s="8" t="str">
         <f aca="false">IF($C22="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C22,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>46138</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>1445</v>
+      </c>
       <c r="F23" s="8" t="str">
         <f aca="false">IF($C23="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C23,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>45490</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>1295</v>
+      </c>
       <c r="F24" s="8" t="str">
         <f aca="false">IF($C24="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C24,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>45700</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>1295</v>
+      </c>
       <c r="F25" s="8" t="str">
         <f aca="false">IF($C25="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C25,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>46140</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>1445</v>
+      </c>
       <c r="F26" s="8" t="str">
         <f aca="false">IF($C26="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C26,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>45869</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>1545</v>
+      </c>
       <c r="F27" s="8" t="str">
         <f aca="false">IF($C27="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C27,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>1447</v>
+      </c>
       <c r="F28" s="8" t="str">
         <f aca="false">IF($C28="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C28,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>45136</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>1475</v>
+      </c>
       <c r="F29" s="8" t="str">
         <f aca="false">IF($C29="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C29,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>46148</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>1465</v>
+      </c>
       <c r="F30" s="8" t="str">
         <f aca="false">IF($C30="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C30,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>45315</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>1425</v>
+      </c>
       <c r="F31" s="8" t="str">
         <f aca="false">IF($C31="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C31,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>46146</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>1465</v>
+      </c>
       <c r="F32" s="8" t="str">
         <f aca="false">IF($C32="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C32,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>45714</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>1325</v>
+      </c>
       <c r="F33" s="8" t="str">
         <f aca="false">IF($C33="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C33,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D34" s="19" t="n">
+        <v>46148</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>1475</v>
+      </c>
       <c r="F34" s="8" t="str">
         <f aca="false">IF($C34="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C34,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>45711</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>1325</v>
+      </c>
       <c r="F35" s="8" t="str">
         <f aca="false">IF($C35="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C35,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>46149</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>1475</v>
+      </c>
       <c r="F36" s="8" t="str">
         <f aca="false">IF($C36="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C36,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>46137</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>1485</v>
+      </c>
       <c r="F37" s="8" t="str">
         <f aca="false">IF($C37="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C37,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D38" s="19" t="n">
+        <v>46163</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>1555</v>
+      </c>
       <c r="F38" s="8" t="str">
         <f aca="false">IF($C38="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C38,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>45664</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>1375</v>
+      </c>
       <c r="F39" s="8" t="str">
         <f aca="false">IF($C39="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C39,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>46243</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>1605</v>
+      </c>
       <c r="F40" s="8" t="str">
         <f aca="false">IF($C40="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C40,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D41" s="19" t="n">
+        <v>45463</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>1295</v>
+      </c>
       <c r="F41" s="8" t="str">
         <f aca="false">IF($C41="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C41,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D42" s="19" t="n">
+        <v>45635</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>1300</v>
+      </c>
       <c r="F42" s="8" t="str">
         <f aca="false">IF($C42="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C42,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D43" s="19" t="n">
+        <v>45634</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>1310</v>
+      </c>
       <c r="F43" s="8" t="str">
         <f aca="false">IF($C43="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C43,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D44" s="19" t="n">
+        <v>45469</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>1325</v>
+      </c>
       <c r="F44" s="8" t="str">
         <f aca="false">IF($C44="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C44,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D45" s="19" t="n">
+        <v>45683</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>1315</v>
+      </c>
       <c r="F45" s="8" t="str">
         <f aca="false">IF($C45="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C45,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D46" s="19" t="n">
+        <v>45303</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>1425</v>
+      </c>
       <c r="F46" s="8" t="str">
         <f aca="false">IF($C46="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C46,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>45686</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>1315</v>
+      </c>
       <c r="F47" s="8" t="str">
         <f aca="false">IF($C47="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C47,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D48" s="19" t="n">
+        <v>45321</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>1425</v>
+      </c>
       <c r="F48" s="8" t="str">
         <f aca="false">IF($C48="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C48,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D49" s="19" t="n">
+        <v>45699</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>1315</v>
+      </c>
       <c r="F49" s="8" t="str">
         <f aca="false">IF($C49="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C49,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D50" s="19" t="n">
+        <v>45711</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>1325</v>
+      </c>
       <c r="F50" s="8" t="str">
         <f aca="false">IF($C50="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C50,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>45326</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>1435</v>
+      </c>
       <c r="F51" s="8" t="str">
         <f aca="false">IF($C51="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C51,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D52" s="19" t="n">
+        <v>45687</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>1325</v>
+      </c>
       <c r="F52" s="8" t="str">
         <f aca="false">IF($C52="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C52,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D53" s="19" t="n">
+        <v>45279</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>1435</v>
+      </c>
       <c r="F53" s="8" t="str">
         <f aca="false">IF($C53="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C53,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D54" s="19" t="n">
+        <v>45683</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>1325</v>
+      </c>
       <c r="F54" s="8" t="str">
         <f aca="false">IF($C54="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C54,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D55" s="19" t="n">
+        <v>45324</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>1435</v>
+      </c>
       <c r="F55" s="8" t="str">
         <f aca="false">IF($C55="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C55,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D56" s="19" t="n">
+        <v>45708</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>1325</v>
+      </c>
       <c r="F56" s="8" t="str">
         <f aca="false">IF($C56="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C56,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D57" s="19" t="n">
+        <v>45129</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>1475</v>
+      </c>
       <c r="F57" s="8" t="str">
         <f aca="false">IF($C57="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C57,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D58" s="19" t="n">
+        <v>45482</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>1325</v>
+      </c>
       <c r="F58" s="8" t="str">
         <f aca="false">IF($C58="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C58,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D59" s="19" t="n">
+        <v>45582</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>1485</v>
+      </c>
       <c r="F59" s="8" t="str">
         <f aca="false">IF($C59="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C59,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D60" s="19" t="n">
+        <v>45711</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>1325</v>
+      </c>
       <c r="F60" s="8" t="str">
         <f aca="false">IF($C60="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C60,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D61" s="19" t="n">
+        <v>45470</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>1335</v>
+      </c>
       <c r="F61" s="8" t="str">
         <f aca="false">IF($C61="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C61,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D62" s="19" t="n">
+        <v>45485</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>1335</v>
+      </c>
       <c r="F62" s="8" t="str">
         <f aca="false">IF($C62="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C62,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D63" s="19" t="n">
+        <v>45476</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>1375</v>
+      </c>
       <c r="F63" s="8" t="str">
         <f aca="false">IF($C63="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C63,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D64" s="19" t="n">
+        <v>45695</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>1365</v>
+      </c>
       <c r="F64" s="8" t="str">
         <f aca="false">IF($C64="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C64,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D65" s="19" t="n">
+        <v>45711</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>1365</v>
+      </c>
       <c r="F65" s="8" t="str">
         <f aca="false">IF($C65="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C65,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D66" s="19" t="n">
+        <v>45468</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>1375</v>
+      </c>
       <c r="F66" s="8" t="str">
         <f aca="false">IF($C66="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C66,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D67" s="19" t="n">
+        <v>45482</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>1375</v>
+      </c>
       <c r="F67" s="8" t="str">
         <f aca="false">IF($C67="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C67,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D68" s="19" t="n">
+        <v>45191</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>1475</v>
+      </c>
       <c r="F68" s="8" t="str">
         <f aca="false">IF($C68="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C68,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D69" s="19" t="n">
+        <v>45617</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>1375</v>
+      </c>
       <c r="F69" s="8" t="str">
         <f aca="false">IF($C69="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C69,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C70" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D70" s="19" t="n">
+        <v>45900</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>1415</v>
+      </c>
       <c r="F70" s="8" t="str">
         <f aca="false">IF($C70="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C70,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D71" s="19" t="n">
+        <v>45663</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>1415</v>
+      </c>
       <c r="F71" s="8" t="str">
         <f aca="false">IF($C71="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C71,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C72" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D72" s="19" t="n">
+        <v>45762</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>1420</v>
+      </c>
       <c r="F72" s="8" t="str">
         <f aca="false">IF($C72="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C72,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D73" s="19" t="n">
+        <v>45609</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>1375</v>
+      </c>
       <c r="F73" s="8" t="str">
         <f aca="false">IF($C73="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C73,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C74" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D74" s="19" t="n">
+        <v>45804</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>1420</v>
+      </c>
       <c r="F74" s="8" t="str">
         <f aca="false">IF($C74="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C74,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C75" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D75" s="19" t="n">
+        <v>45661</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>1375</v>
+      </c>
       <c r="F75" s="8" t="str">
         <f aca="false">IF($C75="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C75,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C76" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D76" s="19" t="n">
+        <v>45941</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>1425</v>
+      </c>
       <c r="F76" s="8" t="str">
         <f aca="false">IF($C76="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C76,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D77" s="19" t="n">
+        <v>45818</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>1430</v>
+      </c>
       <c r="F77" s="8" t="str">
         <f aca="false">IF($C77="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C77,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C78" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D78" s="19" t="n">
+        <v>45759</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>1430</v>
+      </c>
       <c r="F78" s="8" t="str">
         <f aca="false">IF($C78="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C78,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D79" s="19" t="n">
+        <v>45321</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>1435</v>
+      </c>
       <c r="F79" s="8" t="str">
         <f aca="false">IF($C79="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C79,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C80" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D80" s="19" t="n">
+        <v>45632</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>1310</v>
+      </c>
       <c r="F80" s="8" t="str">
         <f aca="false">IF($C80="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C80,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C81" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D81" s="19" t="n">
+        <v>45967</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>1435</v>
+      </c>
       <c r="F81" s="8" t="str">
         <f aca="false">IF($C81="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C81,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C82" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D82" s="19" t="n">
+        <v>45495</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>1405</v>
+      </c>
       <c r="F82" s="8" t="str">
         <f aca="false">IF($C82="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C82,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D83" s="19" t="n">
+        <v>45928</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>1445</v>
+      </c>
       <c r="F83" s="8" t="str">
         <f aca="false">IF($C83="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C83,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C84" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D84" s="19" t="n">
+        <v>45206</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>1475</v>
+      </c>
       <c r="F84" s="8" t="str">
         <f aca="false">IF($C84="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C84,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C85" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D85" s="19" t="n">
+        <v>45493</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>1325</v>
+      </c>
       <c r="F85" s="8" t="str">
         <f aca="false">IF($C85="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C85,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C86" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D86" s="19" t="n">
+        <v>45926</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>1445</v>
+      </c>
       <c r="F86" s="8" t="str">
         <f aca="false">IF($C86="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C86,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C87" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D87" s="19" t="n">
+        <v>45476</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>1335</v>
+      </c>
       <c r="F87" s="8" t="str">
         <f aca="false">IF($C87="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C87,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B88" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C88" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D88" s="19" t="n">
+        <v>45877</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>1399</v>
+      </c>
       <c r="F88" s="8" t="str">
         <f aca="false">IF($C88="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C88,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C89" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D89" s="19" t="n">
+        <v>46130</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>1445</v>
+      </c>
       <c r="F89" s="8" t="str">
         <f aca="false">IF($C89="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C89,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C90" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D90" s="19" t="n">
+        <v>46015</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>1445</v>
+      </c>
       <c r="F90" s="8" t="str">
         <f aca="false">IF($C90="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C90,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B91" s="18"/>
+      <c r="C91" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D91" s="19" t="n">
+        <v>45107</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>1455</v>
+      </c>
       <c r="F91" s="8" t="str">
         <f aca="false">IF($C91="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C91,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="18"/>
+      <c r="C92" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D92" s="19" t="n">
+        <v>45423</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>1425</v>
+      </c>
       <c r="F92" s="8" t="str">
         <f aca="false">IF($C92="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C92,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="18"/>
+      <c r="C93" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D93" s="19" t="n">
+        <v>46017</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>1445</v>
+      </c>
       <c r="F93" s="8" t="str">
         <f aca="false">IF($C93="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C93,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C94" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D94" s="19" t="n">
+        <v>45216</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>1504</v>
+      </c>
       <c r="F94" s="8" t="str">
         <f aca="false">IF($C94="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C94,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B95" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D95" s="19" t="n">
+        <v>46015</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>1455</v>
+      </c>
       <c r="F95" s="8" t="str">
         <f aca="false">IF($C95="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C95,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C96" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D96" s="19" t="n">
+        <v>45402</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>1435</v>
+      </c>
       <c r="F96" s="8" t="str">
         <f aca="false">IF($C96="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C96,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D97" s="19" t="n">
+        <v>46015</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>1455</v>
+      </c>
       <c r="F97" s="8" t="str">
         <f aca="false">IF($C97="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C97,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C98" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D98" s="19" t="n">
+        <v>45424</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>1425</v>
+      </c>
       <c r="F98" s="8" t="str">
         <f aca="false">IF($C98="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C98,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D99" s="19" t="n">
+        <v>46148</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>1465</v>
+      </c>
       <c r="F99" s="8" t="str">
         <f aca="false">IF($C99="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C99,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B100" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C100" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D100" s="19" t="n">
+        <v>45479</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>1375</v>
+      </c>
       <c r="F100" s="8" t="str">
         <f aca="false">IF($C100="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C100,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B101" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C101" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D101" s="19" t="n">
+        <v>45787</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>1470</v>
+      </c>
       <c r="F101" s="8" t="str">
         <f aca="false">IF($C101="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C101,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C102" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D102" s="19" t="n">
+        <v>45791</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>1470</v>
+      </c>
       <c r="F102" s="8" t="str">
         <f aca="false">IF($C102="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C102,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C103" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D103" s="19" t="n">
+        <v>45816</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>1470</v>
+      </c>
       <c r="F103" s="8" t="str">
         <f aca="false">IF($C103="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C103,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C104" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D104" s="19" t="n">
+        <v>45383</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>1435</v>
+      </c>
       <c r="F104" s="8" t="str">
         <f aca="false">IF($C104="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C104,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B105" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C105" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D105" s="19" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>1430</v>
+      </c>
       <c r="F105" s="8" t="str">
         <f aca="false">IF($C105="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C105,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C106" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D106" s="19" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>1475</v>
+      </c>
       <c r="F106" s="8" t="str">
         <f aca="false">IF($C106="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C106,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C107" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D107" s="19" t="n">
+        <v>45240</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>1475</v>
+      </c>
       <c r="F107" s="8" t="str">
         <f aca="false">IF($C107="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C107,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C108" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D108" s="19" t="n">
+        <v>45366</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>1475</v>
+      </c>
       <c r="F108" s="8" t="str">
         <f aca="false">IF($C108="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C108,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C109" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D109" s="19" t="n">
+        <v>45398</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>1475</v>
+      </c>
       <c r="F109" s="8" t="str">
         <f aca="false">IF($C109="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C109,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="C110" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D110" s="19" t="n">
+        <v>45150</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>1475</v>
+      </c>
       <c r="F110" s="8" t="str">
         <f aca="false">IF($C110="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C110,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B111" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C111" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D111" s="19" t="n">
+        <v>45129</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>1525</v>
+      </c>
       <c r="F111" s="8" t="str">
         <f aca="false">IF($C111="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C111,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C112" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D112" s="19" t="n">
+        <v>45940</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>1495</v>
+      </c>
       <c r="F112" s="8" t="str">
         <f aca="false">IF($C112="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C112,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C113" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D113" s="19" t="n">
+        <v>45186</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>1525</v>
+      </c>
       <c r="F113" s="8" t="str">
         <f aca="false">IF($C113="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C113,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C114" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D114" s="19" t="n">
+        <v>45631</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>1275</v>
+      </c>
       <c r="F114" s="8" t="str">
         <f aca="false">IF($C114="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C114,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C115" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D115" s="19" t="n">
+        <v>46015</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>1495</v>
+      </c>
       <c r="F115" s="8" t="str">
         <f aca="false">IF($C115="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C115,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B116" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D116" s="19" t="n">
+        <v>45239</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>1475</v>
+      </c>
       <c r="F116" s="8" t="str">
         <f aca="false">IF($C116="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C116,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B117" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C117" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D117" s="19" t="n">
+        <v>45466</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>1375</v>
+      </c>
       <c r="F117" s="8" t="str">
         <f aca="false">IF($C117="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C117,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C118" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D118" s="19" t="n">
+        <v>45962</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>1495</v>
+      </c>
       <c r="F118" s="8" t="str">
         <f aca="false">IF($C118="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C118,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C119" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D119" s="19" t="n">
+        <v>45849</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>1495</v>
+      </c>
       <c r="F119" s="8" t="str">
         <f aca="false">IF($C119="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C119,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C120" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D120" s="19" t="n">
+        <v>45302</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>1425</v>
+      </c>
       <c r="F120" s="8" t="str">
         <f aca="false">IF($C120="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C120,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C121" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D121" s="19" t="n">
+        <v>45809</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>1420</v>
+      </c>
       <c r="F121" s="8" t="str">
         <f aca="false">IF($C121="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C121,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C122" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D122" s="19" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>1505</v>
+      </c>
       <c r="F122" s="8" t="str">
         <f aca="false">IF($C122="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C122,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C123" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D123" s="19" t="n">
+        <v>45661</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>1415</v>
+      </c>
       <c r="F123" s="8" t="str">
         <f aca="false">IF($C123="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C123,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C124" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D124" s="19" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>1515</v>
+      </c>
       <c r="F124" s="8" t="str">
         <f aca="false">IF($C124="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C124,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C125" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D125" s="19" t="n">
+        <v>45349</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>1475</v>
+      </c>
       <c r="F125" s="8" t="str">
         <f aca="false">IF($C125="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C125,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B126" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C126" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D126" s="19" t="n">
+        <v>45781</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>1470</v>
+      </c>
       <c r="F126" s="8" t="str">
         <f aca="false">IF($C126="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C126,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B127" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C127" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D127" s="19" t="n">
+        <v>46149</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>1515</v>
+      </c>
       <c r="F127" s="8" t="str">
         <f aca="false">IF($C127="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C127,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B128" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C128" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D128" s="19" t="n">
+        <v>45816</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>1430</v>
+      </c>
       <c r="F128" s="8" t="str">
         <f aca="false">IF($C128="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C128,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B129" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C129" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D129" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>1515</v>
+      </c>
       <c r="F129" s="8" t="str">
         <f aca="false">IF($C129="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C129,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B130" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C130" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D130" s="19" t="n">
+        <v>45175</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>1525</v>
+      </c>
       <c r="F130" s="8" t="str">
         <f aca="false">IF($C130="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C130,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B131" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C131" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D131" s="19" t="n">
+        <v>45557</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>1525</v>
+      </c>
       <c r="F131" s="8" t="str">
         <f aca="false">IF($C131="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C131,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B132" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C132" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D132" s="19" t="n">
+        <v>45476</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>1375</v>
+      </c>
       <c r="F132" s="8" t="str">
         <f aca="false">IF($C132="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C132,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B133" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C133" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D133" s="19" t="n">
+        <v>45841</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>1545</v>
+      </c>
       <c r="F133" s="8" t="str">
         <f aca="false">IF($C133="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C133,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B134" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C134" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D134" s="19" t="n">
+        <v>46170</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>1555</v>
+      </c>
       <c r="F134" s="8" t="str">
         <f aca="false">IF($C134="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C134,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B135" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C135" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D135" s="19" t="n">
+        <v>45114</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>1475</v>
+      </c>
       <c r="F135" s="8" t="str">
         <f aca="false">IF($C135="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C135,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B136" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C136" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D136" s="19" t="n">
+        <v>45485</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>1325</v>
+      </c>
       <c r="F136" s="8" t="str">
         <f aca="false">IF($C136="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C136,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B137" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C137" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D137" s="19" t="n">
+        <v>46207</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>1585</v>
+      </c>
       <c r="F137" s="8" t="str">
         <f aca="false">IF($C137="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C137,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B138" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C138" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D138" s="19" t="n">
+        <v>45336</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>1425</v>
+      </c>
       <c r="F138" s="8" t="str">
         <f aca="false">IF($C138="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C138,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B139" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C139" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D139" s="19" t="n">
+        <v>45808</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>1420</v>
+      </c>
       <c r="F139" s="8" t="str">
         <f aca="false">IF($C139="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C139,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B140" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C140" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D140" s="19" t="n">
+        <v>45471</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>1325</v>
+      </c>
       <c r="F140" s="8" t="str">
         <f aca="false">IF($C140="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C140,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B141" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C141" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D141" s="19" t="n">
+        <v>45494</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>1405</v>
+      </c>
       <c r="F141" s="8" t="str">
         <f aca="false">IF($C141="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C141,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B142" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C142" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D142" s="19" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>1485</v>
+      </c>
       <c r="F142" s="8" t="str">
         <f aca="false">IF($C142="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C142,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B143" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C143" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D143" s="19" t="n">
+        <v>45755</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>1430</v>
+      </c>
       <c r="F143" s="8" t="str">
         <f aca="false">IF($C143="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C143,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B144" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C144" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D144" s="19" t="n">
+        <v>45477</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>1335</v>
+      </c>
       <c r="F144" s="8" t="str">
         <f aca="false">IF($C144="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C144,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B145" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C145" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D145" s="19" t="n">
+        <v>45883</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>1399</v>
+      </c>
       <c r="F145" s="8" t="str">
         <f aca="false">IF($C145="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C145,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B146" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C146" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D146" s="19" t="n">
+        <v>45499</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>1480</v>
+      </c>
       <c r="F146" s="8" t="str">
         <f aca="false">IF($C146="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C146,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B147" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C147" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D147" s="19" t="n">
+        <v>45817</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>1470</v>
+      </c>
       <c r="F147" s="8" t="str">
         <f aca="false">IF($C147="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C147,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B148" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C148" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D148" s="19" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>1608</v>
+      </c>
       <c r="F148" s="8" t="str">
         <f aca="false">IF($C148="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C148,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B149" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C149" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D149" s="19" t="n">
+        <v>45566</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>1525</v>
+      </c>
       <c r="F149" s="8" t="str">
         <f aca="false">IF($C149="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C149,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B150" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="C150" s="9" t="n">
+        <v>787</v>
+      </c>
+      <c r="D150" s="19" t="n">
+        <v>45899</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>1495</v>
+      </c>
       <c r="F150" s="8" t="str">
         <f aca="false">IF($C150="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C150,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>1x1-pp</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B151" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C151" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D151" s="19" t="n">
+        <v>45321</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>1665</v>
+      </c>
       <c r="F151" s="8" t="str">
         <f aca="false">IF($C151="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C151,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B152" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C152" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D152" s="19" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>1690</v>
+      </c>
       <c r="F152" s="8" t="str">
         <f aca="false">IF($C152="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C152,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B153" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C153" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D153" s="19" t="n">
+        <v>45106</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>1695</v>
+      </c>
       <c r="F153" s="8" t="str">
         <f aca="false">IF($C153="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C153,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B154" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C154" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D154" s="19" t="n">
+        <v>45888</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>1760</v>
+      </c>
       <c r="F154" s="8" t="str">
         <f aca="false">IF($C154="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C154,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B155" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C155" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D155" s="19" t="n">
+        <v>46103</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>1690</v>
+      </c>
       <c r="F155" s="8" t="str">
         <f aca="false">IF($C155="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C155,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B156" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C156" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D156" s="19" t="n">
+        <v>45098</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>1695</v>
+      </c>
       <c r="F156" s="8" t="str">
         <f aca="false">IF($C156="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C156,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B157" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C157" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D157" s="19" t="n">
+        <v>45606</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>1595</v>
+      </c>
       <c r="F157" s="8" t="str">
         <f aca="false">IF($C157="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C157,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B158" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C158" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D158" s="19" t="n">
+        <v>46144</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>1697</v>
+      </c>
       <c r="F158" s="8" t="str">
         <f aca="false">IF($C158="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C158,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B159" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C159" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D159" s="19" t="n">
+        <v>46141</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>1697</v>
+      </c>
       <c r="F159" s="8" t="str">
         <f aca="false">IF($C159="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C159,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B160" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C160" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D160" s="19" t="n">
+        <v>45672</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>1735</v>
+      </c>
       <c r="F160" s="8" t="str">
         <f aca="false">IF($C160="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C160,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B161" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C161" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D161" s="19" t="n">
+        <v>46117</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>1700</v>
+      </c>
       <c r="F161" s="8" t="str">
         <f aca="false">IF($C161="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C161,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B162" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C162" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D162" s="19" t="n">
+        <v>45424</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>1675</v>
+      </c>
       <c r="F162" s="8" t="str">
         <f aca="false">IF($C162="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C162,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B163" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C163" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D163" s="19" t="n">
+        <v>46137</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>1707</v>
+      </c>
       <c r="F163" s="8" t="str">
         <f aca="false">IF($C163="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C163,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B164" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C164" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D164" s="19" t="n">
+        <v>46127</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>1730</v>
+      </c>
       <c r="F164" s="8" t="str">
         <f aca="false">IF($C164="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C164,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B165" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C165" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D165" s="19" t="n">
+        <v>45627</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>1585</v>
+      </c>
       <c r="F165" s="8" t="str">
         <f aca="false">IF($C165="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C165,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B166" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C166" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D166" s="19" t="n">
+        <v>46146</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>1732</v>
+      </c>
       <c r="F166" s="8" t="str">
         <f aca="false">IF($C166="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C166,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B167" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C167" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D167" s="19" t="n">
+        <v>45273</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>1575</v>
+      </c>
       <c r="F167" s="8" t="str">
         <f aca="false">IF($C167="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C167,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B168" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C168" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D168" s="19" t="n">
+        <v>45693</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>1685</v>
+      </c>
       <c r="F168" s="8" t="str">
         <f aca="false">IF($C168="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C168,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B169" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C169" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D169" s="19" t="n">
+        <v>46158</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>1772</v>
+      </c>
       <c r="F169" s="8" t="str">
         <f aca="false">IF($C169="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C169,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B170" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C170" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D170" s="19" t="n">
+        <v>45754</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>1660</v>
+      </c>
       <c r="F170" s="8" t="str">
         <f aca="false">IF($C170="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C170,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B171" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C171" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D171" s="19" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>1862</v>
+      </c>
       <c r="F171" s="8" t="str">
         <f aca="false">IF($C171="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C171,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B172" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C172" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D172" s="19" t="n">
+        <v>45412</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>1675</v>
+      </c>
       <c r="F172" s="8" t="str">
         <f aca="false">IF($C172="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C172,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B173" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C173" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D173" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>1862</v>
+      </c>
       <c r="F173" s="8" t="str">
         <f aca="false">IF($C173="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C173,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B174" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C174" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D174" s="19" t="n">
+        <v>45766</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>1740</v>
+      </c>
       <c r="F174" s="8" t="str">
         <f aca="false">IF($C174="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C174,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B175" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C175" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D175" s="19" t="n">
+        <v>46187</v>
+      </c>
+      <c r="E175" s="10" t="n">
+        <v>1902</v>
+      </c>
       <c r="F175" s="8" t="str">
         <f aca="false">IF($C175="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C175,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B176" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C176" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D176" s="19" t="n">
+        <v>45630</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>1625</v>
+      </c>
       <c r="F176" s="8" t="str">
         <f aca="false">IF($C176="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C176,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B177" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C177" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D177" s="19" t="n">
+        <v>45750</v>
+      </c>
+      <c r="E177" s="10" t="n">
+        <v>1630</v>
+      </c>
       <c r="F177" s="8" t="str">
         <f aca="false">IF($C177="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C177,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B178" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C178" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D178" s="19" t="n">
+        <v>45741</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>1650</v>
+      </c>
       <c r="F178" s="8" t="str">
         <f aca="false">IF($C178="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C178,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B179" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C179" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D179" s="19" t="n">
+        <v>45321</v>
+      </c>
+      <c r="E179" s="10" t="n">
+        <v>1675</v>
+      </c>
       <c r="F179" s="8" t="str">
         <f aca="false">IF($C179="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C179,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B180" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C180" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D180" s="19" t="n">
+        <v>45707</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>1660</v>
+      </c>
       <c r="F180" s="8" t="str">
         <f aca="false">IF($C180="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C180,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B181" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C181" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D181" s="19" t="n">
+        <v>45745</v>
+      </c>
+      <c r="E181" s="10" t="n">
+        <v>1660</v>
+      </c>
       <c r="F181" s="8" t="str">
         <f aca="false">IF($C181="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C181,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B182" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C182" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D182" s="19" t="n">
+        <v>45181</v>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>1725</v>
+      </c>
       <c r="F182" s="8" t="str">
         <f aca="false">IF($C182="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C182,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B183" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C183" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D183" s="19" t="n">
+        <v>45734</v>
+      </c>
+      <c r="E183" s="10" t="n">
+        <v>1660</v>
+      </c>
       <c r="F183" s="8" t="str">
         <f aca="false">IF($C183="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C183,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B184" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C184" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D184" s="19" t="n">
+        <v>45290</v>
+      </c>
+      <c r="E184" s="10" t="n">
+        <v>1675</v>
+      </c>
       <c r="F184" s="8" t="str">
         <f aca="false">IF($C184="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C184,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B185" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C185" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D185" s="19" t="n">
+        <v>45734</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>1660</v>
+      </c>
       <c r="F185" s="8" t="str">
         <f aca="false">IF($C185="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C185,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B186" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C186" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D186" s="19" t="n">
+        <v>45699</v>
+      </c>
+      <c r="E186" s="10" t="n">
+        <v>1665</v>
+      </c>
       <c r="F186" s="8" t="str">
         <f aca="false">IF($C186="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C186,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B187" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C187" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D187" s="19" t="n">
+        <v>45399</v>
+      </c>
+      <c r="E187" s="10" t="n">
+        <v>1675</v>
+      </c>
       <c r="F187" s="8" t="str">
         <f aca="false">IF($C187="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C187,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B188" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C188" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D188" s="19" t="n">
+        <v>45685</v>
+      </c>
+      <c r="E188" s="10" t="n">
+        <v>1665</v>
+      </c>
       <c r="F188" s="8" t="str">
         <f aca="false">IF($C188="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C188,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B189" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C189" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D189" s="19" t="n">
+        <v>45418</v>
+      </c>
+      <c r="E189" s="10" t="n">
+        <v>1665</v>
+      </c>
       <c r="F189" s="8" t="str">
         <f aca="false">IF($C189="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C189,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B190" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C190" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D190" s="19" t="n">
+        <v>45385</v>
+      </c>
+      <c r="E190" s="10" t="n">
+        <v>1665</v>
+      </c>
       <c r="F190" s="8" t="str">
         <f aca="false">IF($C190="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C190,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B191" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C191" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D191" s="19" t="n">
+        <v>45381</v>
+      </c>
+      <c r="E191" s="10" t="n">
+        <v>1675</v>
+      </c>
       <c r="F191" s="8" t="str">
         <f aca="false">IF($C191="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C191,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B192" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C192" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D192" s="19" t="n">
+        <v>45734</v>
+      </c>
+      <c r="E192" s="10" t="n">
+        <v>1675</v>
+      </c>
       <c r="F192" s="8" t="str">
         <f aca="false">IF($C192="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C192,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B193" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C193" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D193" s="19" t="n">
+        <v>45352</v>
+      </c>
+      <c r="E193" s="10" t="n">
+        <v>1675</v>
+      </c>
       <c r="F193" s="8" t="str">
         <f aca="false">IF($C193="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C193,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B194" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C194" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D194" s="19" t="n">
+        <v>45615</v>
+      </c>
+      <c r="E194" s="10" t="n">
+        <v>1675</v>
+      </c>
       <c r="F194" s="8" t="str">
         <f aca="false">IF($C194="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C194,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B195" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C195" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D195" s="19" t="n">
+        <v>45295</v>
+      </c>
+      <c r="E195" s="10" t="n">
+        <v>1665</v>
+      </c>
       <c r="F195" s="8" t="str">
         <f aca="false">IF($C195="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C195,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B196" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C196" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D196" s="19" t="n">
+        <v>45685</v>
+      </c>
+      <c r="E196" s="10" t="n">
+        <v>1675</v>
+      </c>
       <c r="F196" s="8" t="str">
         <f aca="false">IF($C196="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C196,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B197" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C197" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D197" s="19" t="n">
+        <v>45352</v>
+      </c>
+      <c r="E197" s="10" t="n">
+        <v>1665</v>
+      </c>
       <c r="F197" s="8" t="str">
         <f aca="false">IF($C197="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C197,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B198" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C198" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D198" s="19" t="n">
+        <v>45687</v>
+      </c>
+      <c r="E198" s="10" t="n">
+        <v>1675</v>
+      </c>
       <c r="F198" s="8" t="str">
         <f aca="false">IF($C198="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C198,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B199" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="C199" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D199" s="19" t="n">
+        <v>45095</v>
+      </c>
+      <c r="E199" s="10" t="n">
+        <v>1695</v>
+      </c>
       <c r="F199" s="8" t="str">
         <f aca="false">IF($C199="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C199,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B200" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C200" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D200" s="19" t="n">
+        <v>45524</v>
+      </c>
+      <c r="E200" s="10" t="n">
+        <v>1905</v>
+      </c>
       <c r="F200" s="8" t="str">
         <f aca="false">IF($C200="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C200,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B201" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C201" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D201" s="19" t="n">
+        <v>45753</v>
+      </c>
+      <c r="E201" s="10" t="n">
+        <v>1700</v>
+      </c>
       <c r="F201" s="8" t="str">
         <f aca="false">IF($C201="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C201,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B202" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C202" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D202" s="19" t="n">
+        <v>45325</v>
+      </c>
+      <c r="E202" s="10" t="n">
+        <v>1675</v>
+      </c>
       <c r="F202" s="8" t="str">
         <f aca="false">IF($C202="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C202,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B203" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C203" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D203" s="19" t="n">
+        <v>45771</v>
+      </c>
+      <c r="E203" s="10" t="n">
+        <v>1700</v>
+      </c>
       <c r="F203" s="8" t="str">
         <f aca="false">IF($C203="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C203,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B204" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C204" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D204" s="19" t="n">
+        <v>45309</v>
+      </c>
+      <c r="E204" s="10" t="n">
+        <v>1675</v>
+      </c>
       <c r="F204" s="8" t="str">
         <f aca="false">IF($C204="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C204,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B205" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C205" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D205" s="19" t="n">
+        <v>45756</v>
+      </c>
+      <c r="E205" s="10" t="n">
+        <v>1700</v>
+      </c>
       <c r="F205" s="8" t="str">
         <f aca="false">IF($C205="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C205,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B206" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="C206" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D206" s="19" t="n">
+        <v>45113</v>
+      </c>
+      <c r="E206" s="10" t="n">
+        <v>1705</v>
+      </c>
       <c r="F206" s="8" t="str">
         <f aca="false">IF($C206="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C206,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B207" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C207" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D207" s="19" t="n">
+        <v>45350</v>
+      </c>
+      <c r="E207" s="10" t="n">
+        <v>1715</v>
+      </c>
       <c r="F207" s="8" t="str">
         <f aca="false">IF($C207="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C207,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B208" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C208" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D208" s="19" t="n">
+        <v>45136</v>
+      </c>
+      <c r="E208" s="10" t="n">
+        <v>1765</v>
+      </c>
       <c r="F208" s="8" t="str">
         <f aca="false">IF($C208="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C208,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B209" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C209" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D209" s="19" t="n">
+        <v>45423</v>
+      </c>
+      <c r="E209" s="10" t="n">
+        <v>1715</v>
+      </c>
       <c r="F209" s="8" t="str">
         <f aca="false">IF($C209="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C209,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B210" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="C210" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D210" s="19" t="n">
+        <v>45142</v>
+      </c>
+      <c r="E210" s="10" t="n">
+        <v>1715</v>
+      </c>
       <c r="F210" s="8" t="str">
         <f aca="false">IF($C210="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C210,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B211" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="C211" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D211" s="19" t="n">
+        <v>45164</v>
+      </c>
+      <c r="E211" s="10" t="n">
+        <v>1715</v>
+      </c>
       <c r="F211" s="8" t="str">
         <f aca="false">IF($C211="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C211,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B212" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C212" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D212" s="19" t="n">
+        <v>45425</v>
+      </c>
+      <c r="E212" s="10" t="n">
+        <v>1715</v>
+      </c>
       <c r="F212" s="8" t="str">
         <f aca="false">IF($C212="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C212,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B213" s="18"/>
+      <c r="C213" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D213" s="19" t="n">
+        <v>45321</v>
+      </c>
+      <c r="E213" s="10" t="n">
+        <v>1665</v>
+      </c>
       <c r="F213" s="8" t="str">
         <f aca="false">IF($C213="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C213,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B214" s="18"/>
+      <c r="C214" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D214" s="19" t="n">
+        <v>45715</v>
+      </c>
+      <c r="E214" s="10" t="n">
+        <v>1650</v>
+      </c>
       <c r="F214" s="8" t="str">
         <f aca="false">IF($C214="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C214,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B215" s="18"/>
+      <c r="C215" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D215" s="19" t="n">
+        <v>46017</v>
+      </c>
+      <c r="E215" s="10" t="n">
+        <v>1719</v>
+      </c>
       <c r="F215" s="8" t="str">
         <f aca="false">IF($C215="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C215,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B216" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C216" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D216" s="19" t="n">
+        <v>45104</v>
+      </c>
+      <c r="E216" s="10" t="n">
+        <v>1695</v>
+      </c>
       <c r="F216" s="8" t="str">
         <f aca="false">IF($C216="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C216,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B217" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C217" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D217" s="19" t="n">
+        <v>45679</v>
+      </c>
+      <c r="E217" s="10" t="n">
+        <v>1725</v>
+      </c>
       <c r="F217" s="8" t="str">
         <f aca="false">IF($C217="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C217,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B218" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C218" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D218" s="19" t="n">
+        <v>45894</v>
+      </c>
+      <c r="E218" s="10" t="n">
+        <v>1734</v>
+      </c>
       <c r="F218" s="8" t="str">
         <f aca="false">IF($C218="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C218,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B219" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C219" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D219" s="19" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E219" s="10" t="n">
+        <v>1740</v>
+      </c>
       <c r="F219" s="8" t="str">
         <f aca="false">IF($C219="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C219,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B220" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C220" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D220" s="19" t="n">
+        <v>45766</v>
+      </c>
+      <c r="E220" s="10" t="n">
+        <v>1740</v>
+      </c>
       <c r="F220" s="8" t="str">
         <f aca="false">IF($C220="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C220,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B221" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C221" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D221" s="19" t="n">
+        <v>45490</v>
+      </c>
+      <c r="E221" s="10" t="n">
+        <v>1740</v>
+      </c>
       <c r="F221" s="8" t="str">
         <f aca="false">IF($C221="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C221,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B222" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C222" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D222" s="19" t="n">
+        <v>45769</v>
+      </c>
+      <c r="E222" s="10" t="n">
+        <v>1740</v>
+      </c>
       <c r="F222" s="8" t="str">
         <f aca="false">IF($C222="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C222,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B223" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C223" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D223" s="19" t="n">
+        <v>45762</v>
+      </c>
+      <c r="E223" s="10" t="n">
+        <v>1740</v>
+      </c>
       <c r="F223" s="8" t="str">
         <f aca="false">IF($C223="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C223,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B224" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="C224" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D224" s="19" t="n">
+        <v>45101</v>
+      </c>
+      <c r="E224" s="10" t="n">
+        <v>1745</v>
+      </c>
       <c r="F224" s="8" t="str">
         <f aca="false">IF($C224="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C224,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B225" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C225" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D225" s="19" t="n">
+        <v>46142</v>
+      </c>
+      <c r="E225" s="10" t="n">
+        <v>1747</v>
+      </c>
       <c r="F225" s="8" t="str">
         <f aca="false">IF($C225="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C225,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B226" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C226" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D226" s="19" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E226" s="10" t="n">
+        <v>1755</v>
+      </c>
       <c r="F226" s="8" t="str">
         <f aca="false">IF($C226="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C226,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B227" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C227" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D227" s="19" t="n">
+        <v>45505</v>
+      </c>
+      <c r="E227" s="10" t="n">
+        <v>1855</v>
+      </c>
       <c r="F227" s="8" t="str">
         <f aca="false">IF($C227="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C227,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B228" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C228" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D228" s="19" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E228" s="10" t="n">
+        <v>1762</v>
+      </c>
       <c r="F228" s="8" t="str">
         <f aca="false">IF($C228="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C228,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B229" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C229" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D229" s="19" t="n">
+        <v>45190</v>
+      </c>
+      <c r="E229" s="10" t="n">
+        <v>1715</v>
+      </c>
       <c r="F229" s="8" t="str">
         <f aca="false">IF($C229="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C229,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B230" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C230" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D230" s="19" t="n">
+        <v>45500</v>
+      </c>
+      <c r="E230" s="10" t="n">
+        <v>1755</v>
+      </c>
       <c r="F230" s="8" t="str">
         <f aca="false">IF($C230="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C230,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B231" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C231" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D231" s="19" t="n">
+        <v>45755</v>
+      </c>
+      <c r="E231" s="10" t="n">
+        <v>1650</v>
+      </c>
       <c r="F231" s="8" t="str">
         <f aca="false">IF($C231="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C231,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B232" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C232" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D232" s="19" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E232" s="10" t="n">
+        <v>1762</v>
+      </c>
       <c r="F232" s="8" t="str">
         <f aca="false">IF($C232="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C232,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B233" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="C233" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D233" s="19" t="n">
+        <v>45182</v>
+      </c>
+      <c r="E233" s="10" t="n">
+        <v>1765</v>
+      </c>
       <c r="F233" s="8" t="str">
         <f aca="false">IF($C233="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C233,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B234" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C234" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D234" s="19" t="n">
+        <v>45471</v>
+      </c>
+      <c r="E234" s="10" t="n">
+        <v>1715</v>
+      </c>
       <c r="F234" s="8" t="str">
         <f aca="false">IF($C234="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C234,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B235" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C235" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D235" s="19" t="n">
+        <v>45802</v>
+      </c>
+      <c r="E235" s="10" t="n">
+        <v>1765</v>
+      </c>
       <c r="F235" s="8" t="str">
         <f aca="false">IF($C235="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C235,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B236" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C236" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D236" s="19" t="n">
+        <v>45642</v>
+      </c>
+      <c r="E236" s="10" t="n">
+        <v>1585</v>
+      </c>
       <c r="F236" s="8" t="str">
         <f aca="false">IF($C236="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C236,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B237" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C237" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D237" s="19" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E237" s="10" t="n">
+        <v>1772</v>
+      </c>
       <c r="F237" s="8" t="str">
         <f aca="false">IF($C237="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C237,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B238" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C238" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D238" s="19" t="n">
+        <v>45620</v>
+      </c>
+      <c r="E238" s="10" t="n">
+        <v>1585</v>
+      </c>
       <c r="F238" s="8" t="str">
         <f aca="false">IF($C238="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C238,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B239" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C239" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D239" s="19" t="n">
+        <v>46161</v>
+      </c>
+      <c r="E239" s="10" t="n">
+        <v>1772</v>
+      </c>
       <c r="F239" s="8" t="str">
         <f aca="false">IF($C239="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C239,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B240" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C240" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D240" s="19" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E240" s="10" t="n">
+        <v>1774</v>
+      </c>
       <c r="F240" s="8" t="str">
         <f aca="false">IF($C240="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C240,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B241" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C241" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D241" s="19" t="n">
+        <v>45227</v>
+      </c>
+      <c r="E241" s="10" t="n">
+        <v>1675</v>
+      </c>
       <c r="F241" s="8" t="str">
         <f aca="false">IF($C241="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C241,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B242" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C242" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D242" s="19" t="n">
+        <v>45753</v>
+      </c>
+      <c r="E242" s="10" t="n">
+        <v>1660</v>
+      </c>
       <c r="F242" s="8" t="str">
         <f aca="false">IF($C242="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C242,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B243" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C243" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D243" s="19" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E243" s="10" t="n">
+        <v>1775</v>
+      </c>
       <c r="F243" s="8" t="str">
         <f aca="false">IF($C243="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C243,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B244" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C244" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D244" s="19" t="n">
+        <v>45974</v>
+      </c>
+      <c r="E244" s="10" t="n">
+        <v>1775</v>
+      </c>
       <c r="F244" s="8" t="str">
         <f aca="false">IF($C244="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C244,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B245" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C245" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D245" s="19" t="n">
+        <v>45095</v>
+      </c>
+      <c r="E245" s="10" t="n">
+        <v>1745</v>
+      </c>
       <c r="F245" s="8" t="str">
         <f aca="false">IF($C245="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C245,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B246" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C246" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D246" s="19" t="n">
+        <v>46134</v>
+      </c>
+      <c r="E246" s="10" t="n">
+        <v>1780</v>
+      </c>
       <c r="F246" s="8" t="str">
         <f aca="false">IF($C246="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C246,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B247" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C247" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D247" s="19" t="n">
+        <v>45919</v>
+      </c>
+      <c r="E247" s="10" t="n">
+        <v>1790</v>
+      </c>
       <c r="F247" s="8" t="str">
         <f aca="false">IF($C247="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C247,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B248" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C248" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D248" s="19" t="n">
+        <v>45550</v>
+      </c>
+      <c r="E248" s="10" t="n">
+        <v>1805</v>
+      </c>
       <c r="F248" s="8" t="str">
         <f aca="false">IF($C248="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C248,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B249" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C249" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D249" s="19" t="n">
+        <v>45739</v>
+      </c>
+      <c r="E249" s="10" t="n">
+        <v>1700</v>
+      </c>
       <c r="F249" s="8" t="str">
         <f aca="false">IF($C249="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C249,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B250" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C250" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D250" s="19" t="n">
+        <v>46164</v>
+      </c>
+      <c r="E250" s="10" t="n">
+        <v>1812</v>
+      </c>
       <c r="F250" s="8" t="str">
         <f aca="false">IF($C250="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C250,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B251" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C251" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D251" s="19" t="n">
+        <v>45203</v>
+      </c>
+      <c r="E251" s="10" t="n">
+        <v>1765</v>
+      </c>
       <c r="F251" s="8" t="str">
         <f aca="false">IF($C251="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C251,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B252" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C252" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D252" s="19" t="n">
+        <v>45461</v>
+      </c>
+      <c r="E252" s="10" t="n">
+        <v>1765</v>
+      </c>
       <c r="F252" s="8" t="str">
         <f aca="false">IF($C252="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C252,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B253" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C253" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D253" s="19" t="n">
+        <v>46161</v>
+      </c>
+      <c r="E253" s="10" t="n">
+        <v>1812</v>
+      </c>
       <c r="F253" s="8" t="str">
         <f aca="false">IF($C253="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C253,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B254" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C254" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D254" s="19" t="n">
+        <v>45302</v>
+      </c>
+      <c r="E254" s="10" t="n">
+        <v>1715</v>
+      </c>
       <c r="F254" s="8" t="str">
         <f aca="false">IF($C254="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C254,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B255" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C255" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D255" s="19" t="n">
+        <v>45791</v>
+      </c>
+      <c r="E255" s="10" t="n">
+        <v>1815</v>
+      </c>
       <c r="F255" s="8" t="str">
         <f aca="false">IF($C255="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C255,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B256" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C256" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D256" s="19" t="n">
+        <v>45383</v>
+      </c>
+      <c r="E256" s="10" t="n">
+        <v>1715</v>
+      </c>
       <c r="F256" s="8" t="str">
         <f aca="false">IF($C256="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C256,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B257" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C257" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D257" s="19" t="n">
+        <v>45932</v>
+      </c>
+      <c r="E257" s="10" t="n">
+        <v>1815</v>
+      </c>
       <c r="F257" s="8" t="str">
         <f aca="false">IF($C257="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C257,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B258" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C258" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D258" s="19" t="n">
+        <v>45323</v>
+      </c>
+      <c r="E258" s="10" t="n">
+        <v>1715</v>
+      </c>
       <c r="F258" s="8" t="str">
         <f aca="false">IF($C258="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C258,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B259" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C259" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D259" s="19" t="n">
+        <v>45685</v>
+      </c>
+      <c r="E259" s="10" t="n">
+        <v>1725</v>
+      </c>
       <c r="F259" s="8" t="str">
         <f aca="false">IF($C259="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C259,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B260" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C260" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D260" s="19" t="n">
+        <v>45808</v>
+      </c>
+      <c r="E260" s="10" t="n">
+        <v>1815</v>
+      </c>
       <c r="F260" s="8" t="str">
         <f aca="false">IF($C260="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C260,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B261" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C261" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D261" s="19" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E261" s="10" t="n">
+        <v>1815</v>
+      </c>
       <c r="F261" s="8" t="str">
         <f aca="false">IF($C261="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C261,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B262" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C262" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D262" s="19" t="n">
+        <v>45489</v>
+      </c>
+      <c r="E262" s="10" t="n">
+        <v>1790</v>
+      </c>
       <c r="F262" s="8" t="str">
         <f aca="false">IF($C262="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C262,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B263" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C263" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D263" s="19" t="n">
+        <v>45877</v>
+      </c>
+      <c r="E263" s="10" t="n">
+        <v>1840</v>
+      </c>
       <c r="F263" s="8" t="str">
         <f aca="false">IF($C263="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C263,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B264" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C264" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D264" s="19" t="n">
+        <v>45892</v>
+      </c>
+      <c r="E264" s="10" t="n">
+        <v>1840</v>
+      </c>
       <c r="F264" s="8" t="str">
         <f aca="false">IF($C264="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C264,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B265" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C265" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D265" s="19" t="n">
+        <v>45126</v>
+      </c>
+      <c r="E265" s="10" t="n">
+        <v>1715</v>
+      </c>
       <c r="F265" s="8" t="str">
         <f aca="false">IF($C265="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C265,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B266" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C266" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D266" s="19" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E266" s="10" t="n">
+        <v>1852</v>
+      </c>
       <c r="F266" s="8" t="str">
         <f aca="false">IF($C266="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C266,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B267" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C267" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D267" s="19" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E267" s="10" t="n">
+        <v>1862</v>
+      </c>
       <c r="F267" s="8" t="str">
         <f aca="false">IF($C267="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C267,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B268" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C268" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D268" s="19" t="n">
+        <v>45500</v>
+      </c>
+      <c r="E268" s="10" t="n">
+        <v>1765</v>
+      </c>
       <c r="F268" s="8" t="str">
         <f aca="false">IF($C268="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C268,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B269" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C269" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D269" s="19" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E269" s="10" t="n">
+        <v>1862</v>
+      </c>
       <c r="F269" s="8" t="str">
         <f aca="false">IF($C269="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C269,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B270" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C270" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D270" s="19" t="n">
+        <v>45844</v>
+      </c>
+      <c r="E270" s="10" t="n">
+        <v>1865</v>
+      </c>
       <c r="F270" s="8" t="str">
         <f aca="false">IF($C270="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C270,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B271" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C271" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D271" s="19" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E271" s="10" t="n">
+        <v>1872</v>
+      </c>
       <c r="F271" s="8" t="str">
         <f aca="false">IF($C271="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C271,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B272" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C272" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D272" s="19" t="n">
+        <v>45325</v>
+      </c>
+      <c r="E272" s="10" t="n">
+        <v>1665</v>
+      </c>
       <c r="F272" s="8" t="str">
         <f aca="false">IF($C272="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C272,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B273" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C273" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D273" s="19" t="n">
+        <v>45886</v>
+      </c>
+      <c r="E273" s="10" t="n">
+        <v>1715</v>
+      </c>
       <c r="F273" s="8" t="str">
         <f aca="false">IF($C273="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C273,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B274" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C274" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D274" s="19" t="n">
+        <v>45321</v>
+      </c>
+      <c r="E274" s="10" t="n">
+        <v>1715</v>
+      </c>
       <c r="F274" s="8" t="str">
         <f aca="false">IF($C274="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C274,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B275" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C275" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D275" s="19" t="n">
+        <v>45846</v>
+      </c>
+      <c r="E275" s="10" t="n">
+        <v>1865</v>
+      </c>
       <c r="F275" s="8" t="str">
         <f aca="false">IF($C275="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C275,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B276" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C276" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D276" s="19" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E276" s="10" t="n">
+        <v>1902</v>
+      </c>
       <c r="F276" s="8" t="str">
         <f aca="false">IF($C276="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C276,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B277" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C277" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D277" s="19" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E277" s="10" t="n">
+        <v>1774</v>
+      </c>
       <c r="F277" s="8" t="str">
         <f aca="false">IF($C277="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C277,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B278" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C278" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D278" s="19" t="n">
+        <v>45840</v>
+      </c>
+      <c r="E278" s="10" t="n">
+        <v>1865</v>
+      </c>
       <c r="F278" s="8" t="str">
         <f aca="false">IF($C278="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C278,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B279" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C279" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D279" s="19" t="n">
+        <v>46211</v>
+      </c>
+      <c r="E279" s="10" t="n">
+        <v>1902</v>
+      </c>
       <c r="F279" s="8" t="str">
         <f aca="false">IF($C279="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C279,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B280" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C280" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D280" s="19" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E280" s="10" t="n">
+        <v>1715</v>
+      </c>
       <c r="F280" s="8" t="str">
         <f aca="false">IF($C280="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C280,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B281" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C281" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D281" s="19" t="n">
+        <v>45696</v>
+      </c>
+      <c r="E281" s="10" t="n">
+        <v>1725</v>
+      </c>
       <c r="F281" s="8" t="str">
         <f aca="false">IF($C281="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C281,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B282" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C282" s="9" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D282" s="19" t="n">
+        <v>45899</v>
+      </c>
+      <c r="E282" s="10" t="n">
+        <v>1840</v>
+      </c>
       <c r="F282" s="8" t="str">
         <f aca="false">IF($C282="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C282,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2a-pp</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B283" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C283" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D283" s="19" t="n">
+        <v>45433</v>
+      </c>
+      <c r="E283" s="10" t="n">
+        <v>1835</v>
+      </c>
       <c r="F283" s="8" t="str">
         <f aca="false">IF($C283="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C283,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B284" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C284" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D284" s="19" t="n">
+        <v>45624</v>
+      </c>
+      <c r="E284" s="10" t="n">
+        <v>1620</v>
+      </c>
       <c r="F284" s="8" t="str">
         <f aca="false">IF($C284="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C284,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B285" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C285" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D285" s="19" t="n">
+        <v>46143</v>
+      </c>
+      <c r="E285" s="10" t="n">
+        <v>1742</v>
+      </c>
       <c r="F285" s="8" t="str">
         <f aca="false">IF($C285="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C285,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B286" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C286" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D286" s="19" t="n">
+        <v>45838</v>
+      </c>
+      <c r="E286" s="10" t="n">
+        <v>1835</v>
+      </c>
       <c r="F286" s="8" t="str">
         <f aca="false">IF($C286="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C286,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B287" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C287" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D287" s="19" t="n">
+        <v>46139</v>
+      </c>
+      <c r="E287" s="10" t="n">
+        <v>1742</v>
+      </c>
       <c r="F287" s="8" t="str">
         <f aca="false">IF($C287="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C287,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B288" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C288" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D288" s="19" t="n">
+        <v>45594</v>
+      </c>
+      <c r="E288" s="10" t="n">
+        <v>1645</v>
+      </c>
       <c r="F288" s="8" t="str">
         <f aca="false">IF($C288="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C288,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B289" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C289" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D289" s="19" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E289" s="10" t="n">
+        <v>1745</v>
+      </c>
       <c r="F289" s="8" t="str">
         <f aca="false">IF($C289="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C289,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B290" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C290" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D290" s="19" t="n">
+        <v>46136</v>
+      </c>
+      <c r="E290" s="10" t="n">
+        <v>1752</v>
+      </c>
       <c r="F290" s="8" t="str">
         <f aca="false">IF($C290="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C290,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B291" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C291" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D291" s="19" t="n">
+        <v>45801</v>
+      </c>
+      <c r="E291" s="10" t="n">
+        <v>1655</v>
+      </c>
       <c r="F291" s="8" t="str">
         <f aca="false">IF($C291="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C291,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B292" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C292" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D292" s="19" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E292" s="10" t="n">
+        <v>1760</v>
+      </c>
       <c r="F292" s="8" t="str">
         <f aca="false">IF($C292="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C292,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B293" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C293" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D293" s="19" t="n">
+        <v>45183</v>
+      </c>
+      <c r="E293" s="10" t="n">
+        <v>1895</v>
+      </c>
       <c r="F293" s="8" t="str">
         <f aca="false">IF($C293="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C293,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B294" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C294" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D294" s="19" t="n">
+        <v>45938</v>
+      </c>
+      <c r="E294" s="10" t="n">
+        <v>1790</v>
+      </c>
       <c r="F294" s="8" t="str">
         <f aca="false">IF($C294="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C294,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B295" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C295" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D295" s="19" t="n">
+        <v>46164</v>
+      </c>
+      <c r="E295" s="10" t="n">
+        <v>1817</v>
+      </c>
       <c r="F295" s="8" t="str">
         <f aca="false">IF($C295="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C295,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B296" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C296" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D296" s="19" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E296" s="10" t="n">
+        <v>1817</v>
+      </c>
       <c r="F296" s="8" t="str">
         <f aca="false">IF($C296="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C296,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B297" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C297" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D297" s="19" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E297" s="10" t="n">
+        <v>1827</v>
+      </c>
       <c r="F297" s="8" t="str">
         <f aca="false">IF($C297="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C297,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B298" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C298" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D298" s="19" t="n">
+        <v>45403</v>
+      </c>
+      <c r="E298" s="10" t="n">
+        <v>1795</v>
+      </c>
       <c r="F298" s="8" t="str">
         <f aca="false">IF($C298="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C298,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B299" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C299" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D299" s="19" t="n">
+        <v>45800</v>
+      </c>
+      <c r="E299" s="10" t="n">
+        <v>1795</v>
+      </c>
       <c r="F299" s="8" t="str">
         <f aca="false">IF($C299="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C299,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B300" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C300" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D300" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="E300" s="10" t="n">
+        <v>1897</v>
+      </c>
       <c r="F300" s="8" t="str">
         <f aca="false">IF($C300="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C300,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B301" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C301" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D301" s="19" t="n">
+        <v>45148</v>
+      </c>
+      <c r="E301" s="10" t="n">
+        <v>1895</v>
+      </c>
       <c r="F301" s="8" t="str">
         <f aca="false">IF($C301="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C301,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B302" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C302" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D302" s="19" t="n">
+        <v>45760</v>
+      </c>
+      <c r="E302" s="10" t="n">
+        <v>1830</v>
+      </c>
       <c r="F302" s="8" t="str">
         <f aca="false">IF($C302="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C302,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B303" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C303" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D303" s="19" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E303" s="10" t="n">
+        <v>1907</v>
+      </c>
       <c r="F303" s="8" t="str">
         <f aca="false">IF($C303="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C303,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B304" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C304" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D304" s="19" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E304" s="10" t="n">
+        <v>1695</v>
+      </c>
       <c r="F304" s="8" t="str">
         <f aca="false">IF($C304="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C304,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B305" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C305" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D305" s="19" t="n">
+        <v>45328</v>
+      </c>
+      <c r="E305" s="10" t="n">
+        <v>1695</v>
+      </c>
       <c r="F305" s="8" t="str">
         <f aca="false">IF($C305="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C305,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B306" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C306" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D306" s="19" t="n">
+        <v>45641</v>
+      </c>
+      <c r="E306" s="10" t="n">
+        <v>1695</v>
+      </c>
       <c r="F306" s="8" t="str">
         <f aca="false">IF($C306="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C306,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B307" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C307" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D307" s="19" t="n">
+        <v>45543</v>
+      </c>
+      <c r="E307" s="10" t="n">
+        <v>1775</v>
+      </c>
       <c r="F307" s="8" t="str">
         <f aca="false">IF($C307="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C307,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B308" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C308" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D308" s="19" t="n">
+        <v>45321</v>
+      </c>
+      <c r="E308" s="10" t="n">
+        <v>1835</v>
+      </c>
       <c r="F308" s="8" t="str">
         <f aca="false">IF($C308="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C308,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B309" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C309" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D309" s="19" t="n">
+        <v>45791</v>
+      </c>
+      <c r="E309" s="10" t="n">
+        <v>1795</v>
+      </c>
       <c r="F309" s="8" t="str">
         <f aca="false">IF($C309="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C309,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B310" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C310" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D310" s="19" t="n">
+        <v>45802</v>
+      </c>
+      <c r="E310" s="10" t="n">
+        <v>1805</v>
+      </c>
       <c r="F310" s="8" t="str">
         <f aca="false">IF($C310="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C310,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B311" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C311" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D311" s="19" t="n">
+        <v>45790</v>
+      </c>
+      <c r="E311" s="10" t="n">
+        <v>1805</v>
+      </c>
       <c r="F311" s="8" t="str">
         <f aca="false">IF($C311="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C311,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B312" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C312" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D312" s="19" t="n">
+        <v>45586</v>
+      </c>
+      <c r="E312" s="10" t="n">
+        <v>1635</v>
+      </c>
       <c r="F312" s="8" t="str">
         <f aca="false">IF($C312="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C312,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B313" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C313" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D313" s="19" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E313" s="10" t="n">
+        <v>1807</v>
+      </c>
       <c r="F313" s="8" t="str">
         <f aca="false">IF($C313="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C313,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B314" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C314" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D314" s="19" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E314" s="10" t="n">
+        <v>1835</v>
+      </c>
       <c r="F314" s="8" t="str">
         <f aca="false">IF($C314="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C314,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B315" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C315" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D315" s="19" t="n">
+        <v>46015</v>
+      </c>
+      <c r="E315" s="10" t="n">
+        <v>1810</v>
+      </c>
       <c r="F315" s="8" t="str">
         <f aca="false">IF($C315="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C315,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B316" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C316" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D316" s="19" t="n">
+        <v>45482</v>
+      </c>
+      <c r="E316" s="10" t="n">
+        <v>1835</v>
+      </c>
       <c r="F316" s="8" t="str">
         <f aca="false">IF($C316="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C316,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B317" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C317" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D317" s="19" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E317" s="10" t="n">
+        <v>1835</v>
+      </c>
       <c r="F317" s="8" t="str">
         <f aca="false">IF($C317="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C317,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B318" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C318" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D318" s="19" t="n">
+        <v>45456</v>
+      </c>
+      <c r="E318" s="10" t="n">
+        <v>1835</v>
+      </c>
       <c r="F318" s="8" t="str">
         <f aca="false">IF($C318="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C318,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B319" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C319" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D319" s="19" t="n">
+        <v>45878</v>
+      </c>
+      <c r="E319" s="10" t="n">
+        <v>1835</v>
+      </c>
       <c r="F319" s="8" t="str">
         <f aca="false">IF($C319="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C319,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B320" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C320" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D320" s="19" t="n">
+        <v>45432</v>
+      </c>
+      <c r="E320" s="10" t="n">
+        <v>1835</v>
+      </c>
       <c r="F320" s="8" t="str">
         <f aca="false">IF($C320="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C320,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B321" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C321" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D321" s="19" t="n">
+        <v>45392</v>
+      </c>
+      <c r="E321" s="10" t="n">
+        <v>1845</v>
+      </c>
       <c r="F321" s="8" t="str">
         <f aca="false">IF($C321="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C321,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B322" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C322" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D322" s="19" t="n">
+        <v>45856</v>
+      </c>
+      <c r="E322" s="10" t="n">
+        <v>1845</v>
+      </c>
       <c r="F322" s="8" t="str">
         <f aca="false">IF($C322="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C322,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B323" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C323" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D323" s="19" t="n">
+        <v>45477</v>
+      </c>
+      <c r="E323" s="10" t="n">
+        <v>1845</v>
+      </c>
       <c r="F323" s="8" t="str">
         <f aca="false">IF($C323="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C323,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B324" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C324" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D324" s="19" t="n">
+        <v>45632</v>
+      </c>
+      <c r="E324" s="10" t="n">
+        <v>1620</v>
+      </c>
       <c r="F324" s="8" t="str">
         <f aca="false">IF($C324="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C324,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B325" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C325" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D325" s="19" t="n">
+        <v>46211</v>
+      </c>
+      <c r="E325" s="10" t="n">
+        <v>1897</v>
+      </c>
       <c r="F325" s="8" t="str">
         <f aca="false">IF($C325="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C325,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B326" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C326" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D326" s="19" t="n">
+        <v>45803</v>
+      </c>
+      <c r="E326" s="10" t="n">
+        <v>1805</v>
+      </c>
       <c r="F326" s="8" t="str">
         <f aca="false">IF($C326="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C326,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B327" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C327" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D327" s="19" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E327" s="10" t="n">
+        <v>1907</v>
+      </c>
       <c r="F327" s="8" t="str">
         <f aca="false">IF($C327="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C327,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B328" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C328" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D328" s="19" t="n">
+        <v>45401</v>
+      </c>
+      <c r="E328" s="10" t="n">
+        <v>1695</v>
+      </c>
       <c r="F328" s="8" t="str">
         <f aca="false">IF($C328="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C328,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B329" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C329" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D329" s="19" t="n">
+        <v>45352</v>
+      </c>
+      <c r="E329" s="10" t="n">
+        <v>1865</v>
+      </c>
       <c r="F329" s="8" t="str">
         <f aca="false">IF($C329="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C329,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B330" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="C330" s="9" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D330" s="19" t="n">
+        <v>45756</v>
+      </c>
+      <c r="E330" s="10" t="n">
+        <v>1850</v>
+      </c>
       <c r="F330" s="8" t="str">
         <f aca="false">IF($C330="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C330,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>2x2b-pp</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B331" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C331" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D331" s="19" t="n">
+        <v>45233</v>
+      </c>
+      <c r="E331" s="10" t="n">
+        <v>1865</v>
+      </c>
       <c r="F331" s="8" t="str">
         <f aca="false">IF($C331="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C331,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B332" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C332" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D332" s="19" t="n">
+        <v>45645</v>
+      </c>
+      <c r="E332" s="10" t="n">
+        <v>2160</v>
+      </c>
       <c r="F332" s="8" t="str">
         <f aca="false">IF($C332="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C332,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B333" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C333" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D333" s="19" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E333" s="10" t="n">
+        <v>1920</v>
+      </c>
       <c r="F333" s="8" t="str">
         <f aca="false">IF($C333="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C333,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B334" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C334" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D334" s="19" t="n">
+        <v>45221</v>
+      </c>
+      <c r="E334" s="10" t="n">
+        <v>1865</v>
+      </c>
       <c r="F334" s="8" t="str">
         <f aca="false">IF($C334="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C334,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B335" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C335" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D335" s="19" t="n">
+        <v>45749</v>
+      </c>
+      <c r="E335" s="10" t="n">
+        <v>1985</v>
+      </c>
       <c r="F335" s="8" t="str">
         <f aca="false">IF($C335="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C335,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B336" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C336" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D336" s="19" t="n">
+        <v>46124</v>
+      </c>
+      <c r="E336" s="10" t="n">
+        <v>1920</v>
+      </c>
       <c r="F336" s="8" t="str">
         <f aca="false">IF($C336="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C336,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B337" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C337" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D337" s="19" t="n">
+        <v>45633</v>
+      </c>
+      <c r="E337" s="10" t="n">
+        <v>1895</v>
+      </c>
       <c r="F337" s="8" t="str">
         <f aca="false">IF($C337="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C337,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B338" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C338" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D338" s="19" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E338" s="10" t="n">
+        <v>1930</v>
+      </c>
       <c r="F338" s="8" t="str">
         <f aca="false">IF($C338="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C338,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B339" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C339" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D339" s="19" t="n">
+        <v>45274</v>
+      </c>
+      <c r="E339" s="10" t="n">
+        <v>1865</v>
+      </c>
       <c r="F339" s="8" t="str">
         <f aca="false">IF($C339="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C339,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B340" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C340" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D340" s="19" t="n">
+        <v>46098</v>
+      </c>
+      <c r="E340" s="10" t="n">
+        <v>1934</v>
+      </c>
       <c r="F340" s="8" t="str">
         <f aca="false">IF($C340="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C340,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B341" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C341" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D341" s="19" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E341" s="10" t="n">
+        <v>2080</v>
+      </c>
       <c r="F341" s="8" t="str">
         <f aca="false">IF($C341="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C341,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B342" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C342" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D342" s="19" t="n">
+        <v>46138</v>
+      </c>
+      <c r="E342" s="10" t="n">
+        <v>2117</v>
+      </c>
       <c r="F342" s="8" t="str">
         <f aca="false">IF($C342="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C342,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B343" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C343" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D343" s="19" t="n">
+        <v>45124</v>
+      </c>
+      <c r="E343" s="10" t="n">
+        <v>2015</v>
+      </c>
       <c r="F343" s="8" t="str">
         <f aca="false">IF($C343="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C343,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B344" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C344" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D344" s="19" t="n">
+        <v>45381</v>
+      </c>
+      <c r="E344" s="10" t="n">
+        <v>1865</v>
+      </c>
       <c r="F344" s="8" t="str">
         <f aca="false">IF($C344="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C344,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B345" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C345" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D345" s="19" t="n">
+        <v>45899</v>
+      </c>
+      <c r="E345" s="10" t="n">
+        <v>2160</v>
+      </c>
       <c r="F345" s="8" t="str">
         <f aca="false">IF($C345="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C345,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B346" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C346" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D346" s="19" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E346" s="10" t="n">
+        <v>2184</v>
+      </c>
       <c r="F346" s="8" t="str">
         <f aca="false">IF($C346="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C346,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B347" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C347" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D347" s="19" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E347" s="10" t="n">
+        <v>1875</v>
+      </c>
       <c r="F347" s="8" t="str">
         <f aca="false">IF($C347="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C347,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B348" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C348" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D348" s="19" t="n">
+        <v>45816</v>
+      </c>
+      <c r="E348" s="10" t="n">
+        <v>2170</v>
+      </c>
       <c r="F348" s="8" t="str">
         <f aca="false">IF($C348="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C348,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B349" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C349" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D349" s="19" t="n">
+        <v>45405</v>
+      </c>
+      <c r="E349" s="10" t="n">
+        <v>1875</v>
+      </c>
       <c r="F349" s="8" t="str">
         <f aca="false">IF($C349="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C349,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B350" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C350" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D350" s="19" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E350" s="10" t="n">
+        <v>2233</v>
+      </c>
       <c r="F350" s="8" t="str">
         <f aca="false">IF($C350="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C350,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B351" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C351" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D351" s="19" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E351" s="10" t="n">
+        <v>2233</v>
+      </c>
       <c r="F351" s="8" t="str">
         <f aca="false">IF($C351="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C351,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B352" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C352" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D352" s="19" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E352" s="10" t="n">
+        <v>1865</v>
+      </c>
       <c r="F352" s="8" t="str">
         <f aca="false">IF($C352="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C352,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B353" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C353" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D353" s="19" t="n">
+        <v>45406</v>
+      </c>
+      <c r="E353" s="10" t="n">
+        <v>1865</v>
+      </c>
       <c r="F353" s="8" t="str">
         <f aca="false">IF($C353="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C353,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B354" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C354" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D354" s="19" t="n">
+        <v>45327</v>
+      </c>
+      <c r="E354" s="10" t="n">
+        <v>1865</v>
+      </c>
       <c r="F354" s="8" t="str">
         <f aca="false">IF($C354="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C354,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B355" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C355" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D355" s="19" t="n">
+        <v>45265</v>
+      </c>
+      <c r="E355" s="10" t="n">
+        <v>1875</v>
+      </c>
       <c r="F355" s="8" t="str">
         <f aca="false">IF($C355="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C355,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B356" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C356" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D356" s="19" t="n">
+        <v>45825</v>
+      </c>
+      <c r="E356" s="10" t="n">
+        <v>1875</v>
+      </c>
       <c r="F356" s="8" t="str">
         <f aca="false">IF($C356="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C356,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B357" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C357" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D357" s="19" t="n">
+        <v>45321</v>
+      </c>
+      <c r="E357" s="10" t="n">
+        <v>1875</v>
+      </c>
       <c r="F357" s="8" t="str">
         <f aca="false">IF($C357="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C357,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B358" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C358" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D358" s="19" t="n">
+        <v>45846</v>
+      </c>
+      <c r="E358" s="10" t="n">
+        <v>1925</v>
+      </c>
       <c r="F358" s="8" t="str">
         <f aca="false">IF($C358="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C358,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B359" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C359" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D359" s="19" t="n">
+        <v>45884</v>
+      </c>
+      <c r="E359" s="10" t="n">
+        <v>1955</v>
+      </c>
       <c r="F359" s="8" t="str">
         <f aca="false">IF($C359="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C359,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B360" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C360" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D360" s="19" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E360" s="10" t="n">
+        <v>1875</v>
+      </c>
       <c r="F360" s="8" t="str">
         <f aca="false">IF($C360="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C360,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B361" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C361" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D361" s="19" t="n">
+        <v>45949</v>
+      </c>
+      <c r="E361" s="10" t="n">
+        <v>1970</v>
+      </c>
       <c r="F361" s="8" t="str">
         <f aca="false">IF($C361="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C361,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B362" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C362" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D362" s="19" t="n">
+        <v>45178</v>
+      </c>
+      <c r="E362" s="10" t="n">
+        <v>2015</v>
+      </c>
       <c r="F362" s="8" t="str">
         <f aca="false">IF($C362="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C362,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B363" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C363" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D363" s="19" t="n">
+        <v>45484</v>
+      </c>
+      <c r="E363" s="10" t="n">
+        <v>2025</v>
+      </c>
       <c r="F363" s="8" t="str">
         <f aca="false">IF($C363="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C363,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B364" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C364" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D364" s="19" t="n">
+        <v>45638</v>
+      </c>
+      <c r="E364" s="10" t="n">
+        <v>2035</v>
+      </c>
       <c r="F364" s="8" t="str">
         <f aca="false">IF($C364="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C364,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B365" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C365" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D365" s="19" t="n">
+        <v>45552</v>
+      </c>
+      <c r="E365" s="10" t="n">
+        <v>2125</v>
+      </c>
       <c r="F365" s="8" t="str">
         <f aca="false">IF($C365="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C365,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B366" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C366" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D366" s="19" t="n">
+        <v>45164</v>
+      </c>
+      <c r="E366" s="10" t="n">
+        <v>2015</v>
+      </c>
       <c r="F366" s="8" t="str">
         <f aca="false">IF($C366="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C366,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B367" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C367" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D367" s="19" t="n">
+        <v>45510</v>
+      </c>
+      <c r="E367" s="10" t="n">
+        <v>2225</v>
+      </c>
       <c r="F367" s="8" t="str">
         <f aca="false">IF($C367="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C367,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B368" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C368" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D368" s="19" t="n">
+        <v>45881</v>
+      </c>
+      <c r="E368" s="10" t="n">
+        <v>2160</v>
+      </c>
       <c r="F368" s="8" t="str">
         <f aca="false">IF($C368="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C368,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B369" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C369" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D369" s="19" t="n">
+        <v>45258</v>
+      </c>
+      <c r="E369" s="10" t="n">
+        <v>1865</v>
+      </c>
       <c r="F369" s="8" t="str">
         <f aca="false">IF($C369="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C369,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B370" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C370" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D370" s="19" t="n">
+        <v>45818</v>
+      </c>
+      <c r="E370" s="10" t="n">
+        <v>2160</v>
+      </c>
       <c r="F370" s="8" t="str">
         <f aca="false">IF($C370="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C370,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B371" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C371" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D371" s="19" t="n">
+        <v>45877</v>
+      </c>
+      <c r="E371" s="10" t="n">
+        <v>2160</v>
+      </c>
       <c r="F371" s="8" t="str">
         <f aca="false">IF($C371="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C371,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B372" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C372" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D372" s="19" t="n">
+        <v>45385</v>
+      </c>
+      <c r="E372" s="10" t="n">
+        <v>1875</v>
+      </c>
       <c r="F372" s="8" t="str">
         <f aca="false">IF($C372="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C372,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B373" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C373" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D373" s="19" t="n">
+        <v>45846</v>
+      </c>
+      <c r="E373" s="10" t="n">
+        <v>2170</v>
+      </c>
       <c r="F373" s="8" t="str">
         <f aca="false">IF($C373="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C373,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B374" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C374" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D374" s="19" t="n">
+        <v>45835</v>
+      </c>
+      <c r="E374" s="10" t="n">
+        <v>2170</v>
+      </c>
       <c r="F374" s="8" t="str">
         <f aca="false">IF($C374="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C374,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B375" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C375" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D375" s="19" t="n">
+        <v>45823</v>
+      </c>
+      <c r="E375" s="10" t="n">
+        <v>2180</v>
+      </c>
       <c r="F375" s="8" t="str">
         <f aca="false">IF($C375="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C375,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B376" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C376" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D376" s="19" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E376" s="10" t="n">
+        <v>2184</v>
+      </c>
       <c r="F376" s="8" t="str">
         <f aca="false">IF($C376="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C376,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B377" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C377" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D377" s="19" t="n">
+        <v>45098</v>
+      </c>
+      <c r="E377" s="10" t="n">
+        <v>1995</v>
+      </c>
       <c r="F377" s="8" t="str">
         <f aca="false">IF($C377="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C377,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B378" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C378" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D378" s="19" t="n">
+        <v>46017</v>
+      </c>
+      <c r="E378" s="10" t="n">
+        <v>2135</v>
+      </c>
       <c r="F378" s="8" t="str">
         <f aca="false">IF($C378="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C378,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B379" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C379" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D379" s="19" t="n">
+        <v>45426</v>
+      </c>
+      <c r="E379" s="10" t="n">
+        <v>1875</v>
+      </c>
       <c r="F379" s="8" t="str">
         <f aca="false">IF($C379="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C379,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B380" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C380" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D380" s="19" t="n">
+        <v>45309</v>
+      </c>
+      <c r="E380" s="10" t="n">
+        <v>1865</v>
+      </c>
       <c r="F380" s="8" t="str">
         <f aca="false">IF($C380="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C380,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B381" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C381" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D381" s="19" t="n">
+        <v>45811</v>
+      </c>
+      <c r="E381" s="10" t="n">
+        <v>2010</v>
+      </c>
       <c r="F381" s="8" t="str">
         <f aca="false">IF($C381="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C381,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B382" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="C382" s="9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D382" s="19" t="n">
+        <v>46163</v>
+      </c>
+      <c r="E382" s="10" t="n">
+        <v>2223</v>
+      </c>
       <c r="F382" s="8" t="str">
         <f aca="false">IF($C382="","",IFERROR(INDEX({"1x1-pp";"2x2a-pp";"2x2b-pp";"3x2-pp"},MATCH($C382,{787;1092;1172;1291},0)),""))</f>
-        <v/>
+        <v>3x2-pp</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18320,33 +22886,33 @@
   <sheetData>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="15" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="6" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C7" s="19" t="n">
         <v>46244</v>
@@ -18368,7 +22934,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="8" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C9" s="19" t="n">
         <v>46232</v>
@@ -18379,7 +22945,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C10" s="19" t="n">
         <v>46225</v>
@@ -18390,7 +22956,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="8" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C11" s="19" t="n">
         <v>46204</v>
@@ -18401,7 +22967,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="3" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D12" s="12" t="n">
         <f aca="false">AVERAGE(D7:D11)</f>
@@ -18410,18 +22976,18 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>412</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="8" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C15" s="19" t="n">
         <v>46240</v>
@@ -18432,7 +22998,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="8" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C16" s="19" t="n">
         <v>46231</v>
@@ -18443,7 +23009,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="8" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C17" s="19" t="n">
         <v>46231</v>
@@ -18454,7 +23020,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="8" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C18" s="19" t="n">
         <v>46224</v>
@@ -18476,7 +23042,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="3" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D20" s="12" t="n">
         <f aca="false">AVERAGE(D15:D19)</f>
@@ -18485,18 +23051,18 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="8" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C23" s="19" t="n">
         <v>46235</v>
@@ -18507,7 +23073,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="8" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C24" s="19" t="n">
         <v>46233</v>
@@ -18518,7 +23084,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="8" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C25" s="19" t="n">
         <v>46226</v>
@@ -18540,7 +23106,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="8" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C27" s="19" t="n">
         <v>46202</v>
@@ -18551,7 +23117,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="3" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D28" s="12" t="n">
         <f aca="false">AVERAGE(D23:D27)</f>
@@ -18560,18 +23126,18 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="7" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="8" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C31" s="19" t="n">
         <v>46195</v>
@@ -18615,7 +23181,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="8" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C35" s="19" t="n">
         <v>46129</v>
@@ -18626,7 +23192,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="3" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D36" s="12" t="n">
         <f aca="false">AVERAGE(D31:D35)</f>
@@ -18635,7 +23201,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="6" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18646,12 +23212,12 @@
         <v>5</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="8" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>106</v>
@@ -18663,7 +23229,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="8" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C41" s="9" t="n">
         <v>100</v>
@@ -18675,7 +23241,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="8" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>30</v>
@@ -18687,7 +23253,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="8" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>44</v>
@@ -18699,7 +23265,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="3" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="D44" s="12" t="n">
         <f aca="false">SUMPRODUCT(D40:D43,C40:C43)/SUM(C40:C43)</f>
@@ -18708,7 +23274,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="6" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18719,7 +23285,7 @@
         <v>5</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18823,7 +23389,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="3" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="D57" s="12" t="n">
         <f aca="false">SUMPRODUCT(D48:D56,C48:C56)/SUM(C48:C56)</f>

--- a/knowledge/exhibits/Rent_Chart_Data.xlsx
+++ b/knowledge/exhibits/Rent_Chart_Data.xlsx
@@ -122,16 +122,16 @@
     <t xml:space="preserve">Seasons T90 effective (mix-wtd)</t>
   </si>
   <si>
-    <t xml:space="preserve">Seasons UW mkt rent (yr avg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seasons L5 / UW entry</t>
+    <t xml:space="preserve">Seasons UW market rent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seasons L5 executed (8/4/26)</t>
   </si>
   <si>
     <t xml:space="preserve">Prelude T90 (mix-wtd)</t>
   </si>
   <si>
-    <t xml:space="preserve">Prelude UW rent/occ (yr avg)</t>
+    <t xml:space="preserve">Prelude UW market rent</t>
   </si>
   <si>
     <t xml:space="preserve">Prelude actual in-place</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">Prelude L5 (8/13/26)</t>
   </si>
   <si>
-    <t xml:space="preserve">UW market rents are ANNUAL AVERAGES, plotted at UW-year midpoints: Seasons Y1 (Nov-26..Oct-27) avg $1,885 sits at Apr-27, then +4/4/3.5/3.5/3% steps; Prelude UW = calendar-year averages at Jul-1. Seasons L5 marker 8/4/26 = executed new-lease spot. Actuals: potential rent net LTL /280 from accrual statement.</t>
+    <t xml:space="preserve">UW market rents are period AVERAGES: quarterly (calendar quarters, plotted mid-quarter) through Y1, annual (plotted at UW-year midpoints) beyond. Seasons = updated model Rent &amp; Occ Data row 5: TMG Y1 = 4Q26-3Q27 avg $1,933.28, then +4/4/3.5/3.5/3%. Prelude = Market Rent Summary row 11 (Q4-25 anchor + TMG Y1 calendar-2026 quarters, avg $1,729.6), then CF Market Rent /280/12. Seasons L5 marker 8/4/26 = executed new-lease spot. Actuals: potential rent net LTL /280 from accrual statement.</t>
   </si>
   <si>
     <t xml:space="preserve">Floorplan Mapped</t>
@@ -4908,7 +4908,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:K53"/>
+  <dimension ref="B2:K57"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -5234,194 +5234,200 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="16" t="n">
+        <v>45976</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="16" t="n">
         <v>45991</v>
       </c>
-      <c r="C22" s="17" t="n">
+      <c r="C23" s="17" t="n">
         <f aca="false">T90_Monthly!U16</f>
         <v>1679.63697089947</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D23" s="17" t="n">
         <f aca="false">T90_Monthly!U29</f>
         <v>1419.62533068783</v>
       </c>
-      <c r="G22" s="17" t="n">
+      <c r="G23" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$38=0,"",T90_Monthly!U37)</f>
         <v>1693.68112244898</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="16" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="16" t="n">
         <v>46022</v>
       </c>
-      <c r="C23" s="17" t="n">
+      <c r="C24" s="17" t="n">
         <f aca="false">T90_Monthly!V16</f>
         <v>1676.65393518519</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D24" s="17" t="n">
         <f aca="false">T90_Monthly!V29</f>
         <v>1423.47106481482</v>
       </c>
-      <c r="G23" s="17" t="n">
+      <c r="G24" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$38=0,"",T90_Monthly!V37)</f>
         <v>1703.96031746032</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="16" t="n">
-        <v>46037</v>
-      </c>
-      <c r="I24" s="10" t="n">
-        <v>1668</v>
-      </c>
-    </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="16" t="n">
+        <v>46037</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="16" t="n">
         <v>46053</v>
       </c>
-      <c r="C25" s="17" t="n">
+      <c r="C26" s="17" t="n">
         <f aca="false">T90_Monthly!W16</f>
         <v>1698.00978535354</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D26" s="17" t="n">
         <f aca="false">T90_Monthly!W29</f>
         <v>1476.7086489899</v>
       </c>
-      <c r="G25" s="17" t="n">
+      <c r="G26" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$38=0,"",T90_Monthly!W37)</f>
         <v>1714.91326530612</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="16" t="n">
-        <v>46068</v>
-      </c>
-      <c r="I26" s="10" t="n">
-        <v>1670</v>
-      </c>
-    </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="16" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>1712.3</v>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="16" t="n">
         <v>46081</v>
       </c>
-      <c r="C27" s="17" t="n">
+      <c r="C28" s="17" t="n">
         <f aca="false">T90_Monthly!X16</f>
         <v>1678.38017676768</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D28" s="17" t="n">
         <f aca="false">T90_Monthly!X29</f>
         <v>1516.18080808081</v>
       </c>
-      <c r="G27" s="17" t="n">
+      <c r="G28" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$38=0,"",T90_Monthly!X37)</f>
         <v>1695.69285714286</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="16" t="n">
-        <v>46096</v>
-      </c>
-      <c r="I28" s="10" t="n">
-        <v>1672</v>
-      </c>
-    </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="16" t="n">
+        <v>46096</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="16" t="n">
         <v>46112</v>
       </c>
-      <c r="C29" s="17" t="n">
+      <c r="C30" s="17" t="n">
         <f aca="false">T90_Monthly!Y16</f>
         <v>1722.68074770928</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D30" s="17" t="n">
         <f aca="false">T90_Monthly!Y29</f>
         <v>1580.24360463793</v>
       </c>
-      <c r="G29" s="17" t="n">
+      <c r="G30" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$38=0,"",T90_Monthly!Y37)</f>
         <v>1629.02380952381</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="16" t="n">
-        <v>46127</v>
-      </c>
-      <c r="I30" s="10" t="n">
-        <v>1675</v>
-      </c>
-    </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="16" t="n">
+        <v>46127</v>
+      </c>
+      <c r="I31" s="10" t="n">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="16" t="n">
         <v>46142</v>
       </c>
-      <c r="C31" s="17" t="n">
+      <c r="C32" s="17" t="n">
         <f aca="false">T90_Monthly!Z16</f>
         <v>1763.60901559454</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D32" s="17" t="n">
         <f aca="false">T90_Monthly!Z29</f>
         <v>1627.761024088</v>
       </c>
-      <c r="G31" s="17" t="n">
+      <c r="G32" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$38=0,"",T90_Monthly!Z37)</f>
         <v>1651.61961951447</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="16" t="n">
-        <v>46157</v>
-      </c>
-      <c r="I32" s="10" t="n">
-        <v>1675</v>
-      </c>
-    </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="16" t="n">
+        <v>46157</v>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>1732.2</v>
+      </c>
+      <c r="I33" s="10" t="n">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="16" t="n">
         <v>46173</v>
       </c>
-      <c r="C33" s="17" t="n">
+      <c r="C34" s="17" t="n">
         <f aca="false">T90_Monthly!AA16</f>
         <v>1836.23011525512</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D34" s="17" t="n">
         <f aca="false">T90_Monthly!AA29</f>
         <v>1723.50387852888</v>
       </c>
-      <c r="G33" s="17" t="n">
+      <c r="G34" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$38=0,"",T90_Monthly!AA37)</f>
         <v>1675.61171579743</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="16" t="n">
-        <v>46188</v>
-      </c>
-      <c r="I34" s="10" t="n">
-        <v>1682</v>
-      </c>
-    </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="16" t="n">
+        <v>46188</v>
+      </c>
+      <c r="I35" s="10" t="n">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="16" t="n">
         <v>46203</v>
       </c>
-      <c r="C35" s="17" t="n">
+      <c r="C36" s="17" t="n">
         <f aca="false">T90_Monthly!AB16</f>
         <v>1913.6579423436</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D36" s="17" t="n">
         <f aca="false">T90_Monthly!AB29</f>
         <v>1858.3439056178</v>
       </c>
-      <c r="G35" s="17" t="n">
+      <c r="G36" s="17" t="n">
         <f aca="false">IF(T90_Monthly!$D$38=0,"",T90_Monthly!AB37)</f>
         <v>1707.15951933405</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="16" t="n">
-        <v>46204</v>
-      </c>
-      <c r="H36" s="10" t="n">
-        <v>1668</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5481,113 +5487,148 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="16" t="n">
-        <v>46507</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>1885</v>
+        <v>46249</v>
+      </c>
+      <c r="H41" s="10" t="n">
+        <v>1745.5</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="16" t="n">
-        <v>46569</v>
+        <v>46341</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>1902.2</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>1745</v>
+        <v>1728.5</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="16" t="n">
-        <v>46873</v>
+        <v>46433</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1960</v>
+        <v>1923.1</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="16" t="n">
-        <v>46935</v>
-      </c>
-      <c r="H44" s="10" t="n">
-        <v>1808</v>
+        <v>46522</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>1946.2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="16" t="n">
-        <v>47238</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>2038</v>
+        <v>46569</v>
+      </c>
+      <c r="H45" s="10" t="n">
+        <v>1775.8</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="16" t="n">
-        <v>47300</v>
-      </c>
-      <c r="H46" s="10" t="n">
-        <v>1883</v>
+        <v>46614</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>1961.7</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="16" t="n">
-        <v>47603</v>
+        <v>46873</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>2110</v>
+        <v>2010.6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="16" t="n">
-        <v>47665</v>
+        <v>46935</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>1952</v>
+        <v>1838.2</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="16" t="n">
-        <v>47968</v>
+        <v>47238</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>2184</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="16" t="n">
+        <v>47300</v>
+      </c>
+      <c r="H50" s="10" t="n">
+        <v>1906.7</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="16" t="n">
+        <v>47603</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>2164.2</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="16" t="n">
+        <v>47665</v>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v>1976.5</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="16" t="n">
+        <v>47968</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="16" t="n">
         <v>48334</v>
       </c>
-      <c r="E50" s="10" t="n">
-        <v>2249</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="2" t="s">
+      <c r="E54" s="10" t="n">
+        <v>2307.2</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B56" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B52:K53"/>
+    <mergeCell ref="B56:K57"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/knowledge/exhibits/Rent_Chart_Data.xlsx
+++ b/knowledge/exhibits/Rent_Chart_Data.xlsx
@@ -137,10 +137,10 @@
     <t xml:space="preserve">Prelude actual in-place</t>
   </si>
   <si>
-    <t xml:space="preserve">Prelude L5 (8/13/26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UW market rents are period AVERAGES: quarterly (calendar quarters, plotted mid-quarter) through Y1, annual (plotted at UW-year midpoints) beyond. Seasons = updated model Rent &amp; Occ Data row 5: TMG Y1 = 4Q26-3Q27 avg $1,933.28, then +4/4/3.5/3.5/3%. Prelude = Market Rent Summary row 11 (Q4-25 anchor + TMG Y1 calendar-2026 quarters, avg $1,729.6), then CF Market Rent /280/12. Seasons L5 marker 8/4/26 = executed new-lease spot. Actuals: potential rent net LTL /280 from accrual statement.</t>
+    <t xml:space="preserve">Prelude L5 (acq 12/3/25 + 8/13/26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UW market rents are period AVERAGES: quarterly (calendar quarters, plotted mid-quarter) through Y1, annual (plotted at UW-year midpoints) beyond. Seasons = updated model Rent &amp; Occ Data row 5: TMG Y1 = 4Q26-3Q27 avg $1,933.28, then +4/4/3.5/3.5/3%. Prelude = Market Rent Summary row 11 (Q4-25 anchor + TMG Y1 calendar-2026 quarters, avg $1,729.6), then CF Market Rent /280/12. Seasons L5 marker 8/4/26 = executed new-lease spot. Prelude L5 markers: $1,717.5 at acquisition (Market Rent Summary "L5 New" wtd avg, RR 12/3/25) and $1,810.62 current (RR 8/13/26). Actuals: potential rent net LTL /280 from accrual statement.</t>
   </si>
   <si>
     <t xml:space="preserve">Floorplan Mapped</t>
@@ -5234,7 +5234,19 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="16" t="n">
-        <v>45976</v>
+        <v>45991</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <f aca="false">T90_Monthly!U16</f>
+        <v>1679.63697089947</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <f aca="false">T90_Monthly!U29</f>
+        <v>1419.62533068783</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <f aca="false">IF(T90_Monthly!$D$38=0,"",T90_Monthly!U37)</f>
+        <v>1693.68112244898</v>
       </c>
       <c r="H22" s="10" t="n">
         <v>1693</v>
@@ -5242,19 +5254,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="16" t="n">
-        <v>45991</v>
-      </c>
-      <c r="C23" s="17" t="n">
-        <f aca="false">T90_Monthly!U16</f>
-        <v>1679.63697089947</v>
-      </c>
-      <c r="D23" s="17" t="n">
-        <f aca="false">T90_Monthly!U29</f>
-        <v>1419.62533068783</v>
-      </c>
-      <c r="G23" s="17" t="n">
-        <f aca="false">IF(T90_Monthly!$D$38=0,"",T90_Monthly!U37)</f>
-        <v>1693.68112244898</v>
+        <v>45994</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>1717.5</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5303,9 +5306,6 @@
       <c r="B27" s="16" t="n">
         <v>46068</v>
       </c>
-      <c r="H27" s="10" t="n">
-        <v>1712.3</v>
-      </c>
       <c r="I27" s="10" t="n">
         <v>1670</v>
       </c>
@@ -5326,6 +5326,9 @@
         <f aca="false">IF(T90_Monthly!$D$38=0,"",T90_Monthly!X37)</f>
         <v>1695.69285714286</v>
       </c>
+      <c r="H28" s="10" t="n">
+        <v>1712.3</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="16" t="n">
@@ -5381,9 +5384,6 @@
       <c r="B33" s="16" t="n">
         <v>46157</v>
       </c>
-      <c r="H33" s="10" t="n">
-        <v>1732.2</v>
-      </c>
       <c r="I33" s="10" t="n">
         <v>1675</v>
       </c>
@@ -5404,6 +5404,9 @@
         <f aca="false">IF(T90_Monthly!$D$38=0,"",T90_Monthly!AA37)</f>
         <v>1675.61171579743</v>
       </c>
+      <c r="H34" s="10" t="n">
+        <v>1732.2</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="16" t="n">
@@ -5487,7 +5490,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="16" t="n">
-        <v>46249</v>
+        <v>46265</v>
       </c>
       <c r="H41" s="10" t="n">
         <v>1745.5</v>
@@ -5495,7 +5498,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="16" t="n">
-        <v>46341</v>
+        <v>46356</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>1902.2</v>
@@ -5506,7 +5509,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="16" t="n">
-        <v>46433</v>
+        <v>46446</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>1923.1</v>
@@ -5514,7 +5517,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="16" t="n">
-        <v>46522</v>
+        <v>46538</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>1946.2</v>
@@ -5530,7 +5533,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="16" t="n">
-        <v>46614</v>
+        <v>46630</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>1961.7</v>

--- a/knowledge/exhibits/Rent_Chart_Data.xlsx
+++ b/knowledge/exhibits/Rent_Chart_Data.xlsx
@@ -5502,7 +5502,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:L57"/>
+  <dimension ref="B2:L58"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -6299,29 +6299,24 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="16" t="n">
+        <v>48030</v>
+      </c>
+      <c r="I54" s="10" t="n">
+        <v>2045.2</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="16" t="n">
         <v>48334</v>
       </c>
-      <c r="E54" s="10" t="n">
+      <c r="E55" s="10" t="n">
         <v>2307.2</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="2" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B57" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-      <c r="L56" s="2"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
@@ -6333,9 +6328,22 @@
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
     </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B56:L57"/>
+    <mergeCell ref="B57:L58"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
